--- a/Magic_B2B_Prospecting_FL_Highlighted.xlsx
+++ b/Magic_B2B_Prospecting_FL_Highlighted.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="0" xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="23385" tabRatio="0" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Prospecting List" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FL Highlights Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Prospecting List" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="25">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -173,8 +174,23 @@
       <b val="1"/>
       <color rgb="FF006100"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF9C5700"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill/>
     </fill>
@@ -358,6 +374,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -552,7 +574,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -581,13 +603,20 @@
     <xf numFmtId="164" fontId="19" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="33" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="33" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="19" fillId="33" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="19" fillId="33" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -595,6 +624,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="19" fillId="33" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="34" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="34" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="33" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="33" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="34" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="34" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1208,6 +1264,139 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Florida-Connected B2B Prospects</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HQ in FL, dedicated FL business unit/subsidiary, multiple FL offices/branches as a top market, or FL explicitly cited as a strategic market</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Some FL operational presence (1-2 offices, regional rep coverage, distribution touch-point) but FL is one of many markets — not dominant</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>YES — 111 (28 HQ'd in FL + 83 with major FL operations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EDGE — 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NO — remaining rows (no meaningful FL connection)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Methodology notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Pass 1: auto-tagged all 29 companies with HQ listed in Florida (incl. Waste Pro USA — manual correction).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Pass 2: dispatched 6 parallel research agents to assess the remaining ~177 non-FL-HQ companies for major FL operations (multiple FL offices/branches, FL-based subsidiary, FL acquisition history, FL named as top market).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>YES = strong evidence FL is a top-tier operational market. EDGE = some FL presence (1-2 offices, regional coverage) but not dominant. NO = no meaningful FL connection beyond standard nationwide footprint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Data corrections: Waste Pro USA HQ is Longwood, FL (source listed 'United States'); Binance YES applies only to Binance.US (Miami) — global Binance.com is a separate entity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>For large Fortune 500 companies (JPM, Sysco, GEICO, Spectrum, Toll Brothers), YES required dedicated FL workforce/asset evidence beyond just nationwide operations.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H207"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
@@ -1218,7 +1407,7 @@
     <col width="15.5" bestFit="1" customWidth="1" min="5" max="5"/>
     <col width="19.625" bestFit="1" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="95" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -1260,26 +1449,36 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>JPMorganChase</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>Commercial Banking</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="E3" s="9" t="n">
+      <c r="E3" s="16" t="n">
         <v>181800000000</v>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="F3" s="16" t="n">
         <v>60000000000</v>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H3" s="18" t="inlineStr">
+        <is>
+          <t>16,400 FL employees; 400+ branches; 6.2M FL customers; doubling Miami Brickell office; new offices in West Palm Beach, Melbourne, Sarasota, Fort Myers</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -1306,141 +1505,201 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Sysco</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>Food &amp; Beverage Products</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Houston, TX</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="19" t="n">
         <v>81400000000</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="19" t="n">
         <v>13800000000</v>
       </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>~5,000 FL employees; 6 broadline FL facilities; new 504k sqft Plant City DC; South RDC redistribution hub</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>Caterpillar Inc.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>Industrial Machinery</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>Irving, TX</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="21" t="n">
         <v>67599999999</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="21" t="n">
         <v>7000000000</v>
       </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>Miami Lakes Parts Distribution Center serves South FL + Caribbean/Central/South America</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>GEICO</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>Chevy Chase, MD</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="19" t="n">
         <v>50500000000</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="19" t="n">
         <v>3300000000</v>
       </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>~3,800 FL employees; Lakeland + Jacksonville regional offices; new Tampa campus adding 1,000+ jobs</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Spectrum</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>Telecommunications</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>Stamford, CT</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="24" t="n">
         <v>33200000000</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="24" t="n">
         <v>4000000000</v>
       </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
+          <t>Regional ops managed from Clearwater; ops centers in Maitland, Heathrow, Tampa, Orlando, St. Pete, West Palm Beach, Auburndale</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Adecco</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>Zurich, Switzerland</t>
         </is>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="19" t="n">
         <v>23700000000</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="19" t="n">
         <v>2200000000</v>
       </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>Jacksonville is a major business services center (600+ employees) + 20+ FL branches</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>Smurfit Westrock</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>Specialty Manufacturing</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>Clonskeagh, Ireland</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="24" t="n">
         <v>21100000000</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="24" t="n">
         <v>1300000000</v>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>7 plants/offices across Jacksonville + Fernandina Beach incl. 950k-ton Fernandina containerboard mill</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1467,48 +1726,58 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>Roseland, NJ</t>
         </is>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="26" t="n">
         <v>20600000000</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="26" t="n">
         <v>4099999999</v>
       </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>2 large Maitland (Lucien Way) client service campuses + Miami offices</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>Acosta</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>Specialty Retail</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="24" t="inlineStr">
         <is>
           <t>Jacksonville, FL</t>
         </is>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E13" s="24" t="n">
         <v>12200000000</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="F13" s="24" t="n">
         <v>1000000000</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -1516,148 +1785,208 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H13" s="13" t="inlineStr">
+      <c r="H13" s="18" t="inlineStr">
         <is>
           <t>HQ in Jacksonville, FL</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>Toll Brothers</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>Real Estate Development</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>Fort Washington, PA</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="19" t="n">
         <v>11000000000</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="19" t="n">
         <v>1000000000</v>
       </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>FL is a strategic growth state; communities in Parkland, Boca Raton, Jupiter, Palm Beach Gardens, Delray, Flagler, Orlando/Lake Nona, Lakewood Ranch, SW FL</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>FrieslandCampina</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>Food Manufacturing &amp; Processing</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="19" t="inlineStr">
         <is>
           <t>Amersfoort, Netherlands</t>
         </is>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="19" t="n">
         <v>10100000000</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="19" t="n">
         <v>607800000</v>
       </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>Latin American regional HQ in Coral Gables, FL</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Renewal by Andersen</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>Construction &amp; Engineering</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>Cottage Grove, MN</t>
         </is>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="19" t="n">
         <v>9700000000</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="19" t="n">
         <v>559500000</v>
       </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="inlineStr">
+        <is>
+          <t>Dedicated FL franchise division (Mellick Group / RBA of Florida) — Central, North, Tampa/Gulf Coast, SW FL showrooms</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>Waste Connections</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t>Waste Management Services</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>Spring, TX</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" s="24" t="n">
         <v>9500000000</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="F17" s="24" t="n">
         <v>959500000</v>
       </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>Heart of Florida Landfill, SLD Landfill (Punta Gorda), Pasco/Sarasota/Clearwater ops + acquisitions of Florida Express Environmental and Great Waste</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Xylem</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>Specialty Manufacturing</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="26" t="inlineStr">
         <is>
           <t>Washington, D.C.</t>
         </is>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="26" t="n">
         <v>9000000000</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="26" t="n">
         <v>1900000000</v>
       </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>FL locations in Apopka, Miami, Pompano Beach, Tallahassee, St. Petersburg (via AMJ)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Binance</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>IT Services</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t>Malta</t>
         </is>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="19" t="n">
         <v>8500000000</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="19" t="n">
         <v>545400000</v>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>Binance.US HQ at 252 NW 29th St, Miami (note: Binance.com global is separate)</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1707,49 +2036,69 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>Insight Global</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="19" t="n">
         <v>6600000000</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="F22" s="19" t="n">
         <v>303700000</v>
       </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H22" s="18" t="inlineStr">
+        <is>
+          <t>Major FL branches in Miami (Brickell), Tampa (Midtown), Jacksonville (Gate Pkwy); FL is a top staffing market</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>First American</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="27" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="26" t="inlineStr">
         <is>
           <t>Santa Ana, CA</t>
         </is>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="26" t="n">
         <v>6100000000</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="26" t="n">
         <v>520299999</v>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H23" s="23" t="inlineStr">
+        <is>
+          <t>Many FL title offices (Orlando, Tampa, Brandon, New Tampa, Boynton, Maitland, Lake Worth)</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1799,26 +2148,36 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>Robert Half</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="27" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="26" t="inlineStr">
         <is>
           <t>Menlo Park, CA</t>
         </is>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="26" t="n">
         <v>5400000000</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="F26" s="26" t="n">
         <v>1900000000</v>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H26" s="23" t="inlineStr">
+        <is>
+          <t>Multiple FL offices (2 Miami, 2 Tampa, Jacksonville + more)</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1868,25 +2227,25 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>Interim HealthCare Inc.</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>Healthcare Providers</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D29" s="19" t="inlineStr">
         <is>
           <t>Sunrise, FL</t>
         </is>
       </c>
-      <c r="E29" s="14" t="n">
+      <c r="E29" s="19" t="n">
         <v>5300000000</v>
       </c>
-      <c r="F29" s="14" t="n">
+      <c r="F29" s="19" t="n">
         <v>352600000</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
@@ -1894,56 +2253,76 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H29" s="13" t="inlineStr">
+      <c r="H29" s="18" t="inlineStr">
         <is>
           <t>HQ in Sunrise, FL</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>Intertek</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>Operating Systems &amp; Utility Software</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="19" t="inlineStr">
         <is>
           <t>London, United Kingdom</t>
         </is>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="19" t="n">
         <v>4300000000</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="19" t="n">
         <v>561900000</v>
       </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H30" s="18" t="inlineStr">
+        <is>
+          <t>Intertek PSI: facilities in Miami, Orlando, Pensacola, Plant City, Riviera Beach, Tampa + FL petroleum/chemical labs</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>Kelly</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>Troy, MI</t>
         </is>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="E31" s="21" t="n">
         <v>4300000000</v>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="F31" s="21" t="n">
         <v>281600000</v>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H31" s="23" t="inlineStr">
+        <is>
+          <t>Multiple FL offices (Tampa, Orlando, Miami Lakes, Tallahassee, Jacksonville)</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1970,25 +2349,25 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>ARCO Murray Construction Company</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>Construction &amp; Engineering</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="E33" s="14" t="n">
+      <c r="E33" s="19" t="n">
         <v>4300000000</v>
       </c>
-      <c r="F33" s="14" t="n">
+      <c r="F33" s="19" t="n">
         <v>257800000</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
@@ -1996,78 +2375,98 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H33" s="13" t="inlineStr">
+      <c r="H33" s="18" t="inlineStr">
         <is>
           <t>HQ in Orlando, FL</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="26" t="inlineStr">
         <is>
           <t>Convergint</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="27" t="inlineStr">
         <is>
           <t>Security Technology</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="26" t="inlineStr">
         <is>
           <t>Schaumburg, IL</t>
         </is>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="26" t="n">
         <v>4099999999</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="F34" s="26" t="n">
         <v>250000000</v>
       </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H34" s="23" t="inlineStr">
+        <is>
+          <t>Acquired Fort Myers-based Fiber Solutions (May 2025) + Orlando location via Operational Security Systems</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="24" t="inlineStr">
         <is>
           <t>Ferraro Foods</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="25" t="inlineStr">
         <is>
           <t>Food &amp; Beverage Technology</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="24" t="inlineStr">
         <is>
           <t>Piscataway, NJ</t>
         </is>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="E35" s="24" t="n">
         <v>4099999999</v>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="F35" s="24" t="n">
         <v>263899999</v>
       </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H35" s="18" t="inlineStr">
+        <is>
+          <t>Acquired Cremosa + New Crem Flora Foods (FL, 2021) — FL is one of six operating-state regions</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>Travel + Leisure Co.</t>
         </is>
       </c>
-      <c r="C36" s="15" t="inlineStr">
+      <c r="C36" s="20" t="inlineStr">
         <is>
           <t>Travel &amp; Tourism Services</t>
         </is>
       </c>
-      <c r="D36" s="14" t="inlineStr">
+      <c r="D36" s="19" t="inlineStr">
         <is>
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="E36" s="14" t="n">
+      <c r="E36" s="19" t="n">
         <v>4000000000</v>
       </c>
-      <c r="F36" s="14" t="n">
+      <c r="F36" s="19" t="n">
         <v>1100000000</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
@@ -2075,7 +2474,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H36" s="13" t="inlineStr">
+      <c r="H36" s="18" t="inlineStr">
         <is>
           <t>HQ in Orlando, FL</t>
         </is>
@@ -2105,233 +2504,333 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="24" t="inlineStr">
         <is>
           <t>Alro Steel</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="25" t="inlineStr">
         <is>
           <t>Metal Fabrication</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" s="24" t="inlineStr">
         <is>
           <t>Jackson, MI</t>
         </is>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="E38" s="24" t="n">
         <v>3100000000</v>
       </c>
-      <c r="F38" s="2" t="n">
+      <c r="F38" s="24" t="n">
         <v>166700000</v>
       </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H38" s="18" t="inlineStr">
+        <is>
+          <t>6+ FL locations: Orlando (93k sqft), Boca Raton (89k sqft), Tampa, Pompano Beach, Winter Springs, Sarasota</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="19" t="inlineStr">
         <is>
           <t>Stewart Title</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" s="20" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="19" t="inlineStr">
         <is>
           <t>Houston, TX</t>
         </is>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="19" t="n">
         <v>2900000000</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="F39" s="19" t="n">
         <v>830600000</v>
       </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H39" s="18" t="inlineStr">
+        <is>
+          <t>FL agency network in Fort Myers, Tampa, St. Pete, Kissimmee, St. Cloud, West Palm Beach + Townsend Title acquisition (2023); dedicated SVP Florida Agency District</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t>BrightView Landscapes</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" s="20" t="inlineStr">
         <is>
           <t>Utility Services &amp; Equipment</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="19" t="inlineStr">
         <is>
           <t>Blue Bell, PA</t>
         </is>
       </c>
-      <c r="E40" s="4" t="n">
+      <c r="E40" s="19" t="n">
         <v>2800000000</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="F40" s="19" t="n">
         <v>110700000</v>
       </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H40" s="18" t="inlineStr">
+        <is>
+          <t>Major FL acquisitions: Girard Environmental Services (Sanford, FL — 9 branches, ~450 employees), Luke's Landscaping (South FL ~250 employees), West Bay Landscape (Bradenton)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>Korn Ferry</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" s="27" t="inlineStr">
         <is>
           <t>Management &amp; Strategy Consulting</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="26" t="inlineStr">
         <is>
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="26" t="n">
         <v>2800000000</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="F41" s="26" t="n">
         <v>2000000000</v>
       </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H41" s="23" t="inlineStr">
+        <is>
+          <t>Offices in Miami (200 S Biscayne Blvd) and Tampa</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" s="24" t="inlineStr">
         <is>
           <t>Northern Tool + Equipment</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="25" t="inlineStr">
         <is>
           <t>Specialty Retail</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" s="24" t="inlineStr">
         <is>
           <t>Burnsville, MN</t>
         </is>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="E42" s="24" t="n">
         <v>2500000000</v>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="F42" s="24" t="n">
         <v>177500000</v>
       </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H42" s="18" t="inlineStr">
+        <is>
+          <t>10+ FL stores: Cutler Ridge, Orlando, Lakeland, Miami Gardens, Tampa, Ocala, Sarasota, N. Fort Myers, Jacksonville, Casselberry</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="26" t="inlineStr">
         <is>
           <t>WillScot</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" s="27" t="inlineStr">
         <is>
           <t>Commercial Services</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="26" t="inlineStr">
         <is>
           <t>Phoenix, Arizona</t>
         </is>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" s="26" t="n">
         <v>2400000000</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="F43" s="26" t="n">
         <v>143700000</v>
       </c>
+      <c r="G43" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H43" s="23" t="inlineStr">
+        <is>
+          <t>FL branches in Tampa, West Palm Beach, Gainesville, Fort Pierce, Pensacola, Bradenton, Fort Myers</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" s="19" t="inlineStr">
         <is>
           <t>TTEC</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" s="20" t="inlineStr">
         <is>
           <t>Consulting &amp; Outsourcing</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="19" t="inlineStr">
         <is>
           <t>Greenwood Village, CO</t>
         </is>
       </c>
-      <c r="E44" s="4" t="n">
+      <c r="E44" s="19" t="n">
         <v>2200000000</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="F44" s="19" t="n">
         <v>143500000</v>
       </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H44" s="18" t="inlineStr">
+        <is>
+          <t>Centers in Orlando + Melbourne; operations across 17 FL cities; Rockledge customer experience center for healthcare</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" s="26" t="inlineStr">
         <is>
           <t>Actalent</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="27" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="26" t="inlineStr">
         <is>
           <t>Hanover, MD</t>
         </is>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" s="26" t="n">
         <v>2200000000</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="F45" s="26" t="n">
         <v>140500000</v>
       </c>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H45" s="23" t="inlineStr">
+        <is>
+          <t>Offices in Jacksonville, Tampa, Maitland (Orlando), Pensacola</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="24" t="inlineStr">
         <is>
           <t>Performance Foodservice</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="25" t="inlineStr">
         <is>
           <t>Food &amp; Beverage Wholesalers</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" s="24" t="inlineStr">
         <is>
           <t>Richmond, VA</t>
         </is>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="E46" s="24" t="n">
         <v>2100000000</v>
       </c>
-      <c r="F46" s="2" t="n">
+      <c r="F46" s="24" t="n">
         <v>147200000</v>
       </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H46" s="18" t="inlineStr">
+        <is>
+          <t>Empire DC in Miami (66k sqft, 135+ associates); Orlando, Tampa operations; 2024 Cheney Bros. acquisition added 5 FL/GA/AL DCs</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B47" s="19" t="inlineStr">
         <is>
           <t>AppleOne Employment Services</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="20" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="19" t="inlineStr">
         <is>
           <t>Glendale, CA</t>
         </is>
       </c>
-      <c r="E47" s="4" t="n">
+      <c r="E47" s="19" t="n">
         <v>2100000000</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="F47" s="19" t="n">
         <v>135300000</v>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H47" s="18" t="inlineStr">
+        <is>
+          <t>9+ FL offices: Tampa (2), South Orlando, Altamonte Springs, Miami, Boca Raton, Fort Lauderdale, Jacksonville</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -2358,25 +2857,25 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="14" t="inlineStr">
+      <c r="B49" s="19" t="inlineStr">
         <is>
           <t>Castle Group</t>
         </is>
       </c>
-      <c r="C49" s="15" t="inlineStr">
+      <c r="C49" s="20" t="inlineStr">
         <is>
           <t>Land Real Estate</t>
         </is>
       </c>
-      <c r="D49" s="14" t="inlineStr">
+      <c r="D49" s="19" t="inlineStr">
         <is>
           <t>Plantation, FL</t>
         </is>
       </c>
-      <c r="E49" s="14" t="n">
+      <c r="E49" s="19" t="n">
         <v>1600000000</v>
       </c>
-      <c r="F49" s="14" t="n">
+      <c r="F49" s="19" t="n">
         <v>71300000</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
@@ -2384,78 +2883,98 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H49" s="13" t="inlineStr">
+      <c r="H49" s="18" t="inlineStr">
         <is>
           <t>HQ in Plantation, FL</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="21" t="inlineStr">
         <is>
           <t>HID</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="22" t="inlineStr">
         <is>
           <t>Security Technology</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" s="21" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="E50" s="2" t="n">
+      <c r="E50" s="21" t="n">
         <v>1500000000</v>
       </c>
-      <c r="F50" s="2" t="n">
+      <c r="F50" s="21" t="n">
         <v>87500000</v>
       </c>
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H50" s="23" t="inlineStr">
+        <is>
+          <t>Offices in Palm Beach Gardens and Tampa</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" s="19" t="inlineStr">
         <is>
           <t>EquipmentShare</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="20" t="inlineStr">
         <is>
           <t>Construction &amp; Engineering</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D51" s="19" t="inlineStr">
         <is>
           <t>Columbia, MO</t>
         </is>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="E51" s="19" t="n">
         <v>1500000000</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="F51" s="19" t="n">
         <v>72000000</v>
       </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H51" s="18" t="inlineStr">
+        <is>
+          <t>10+ FL branches: Orlando (2), Hialeah, Tampa, Fort Myers, Jacksonville (2), Alachua, West Palm Beach, Pensacola, Ocala</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="B52" s="14" t="inlineStr">
+      <c r="B52" s="19" t="inlineStr">
         <is>
           <t>Waste Pro USA</t>
         </is>
       </c>
-      <c r="C52" s="15" t="inlineStr">
+      <c r="C52" s="20" t="inlineStr">
         <is>
           <t>Utility Services &amp; Equipment</t>
         </is>
       </c>
-      <c r="D52" s="14" t="inlineStr">
+      <c r="D52" s="19" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E52" s="14" t="n">
+      <c r="E52" s="19" t="n">
         <v>1500000000</v>
       </c>
-      <c r="F52" s="14" t="n">
+      <c r="F52" s="19" t="n">
         <v>95700000</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
@@ -2463,9 +2982,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H52" s="13" t="inlineStr">
-        <is>
-          <t>HQ in Longwood, FL (HQ correction — listed as 'United States' in source)</t>
+      <c r="H52" s="18" t="inlineStr">
+        <is>
+          <t>HQ in Longwood, FL (data correction — original source listed 'United States'); founded 2001 in FL</t>
         </is>
       </c>
     </row>
@@ -2539,49 +3058,69 @@
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B56" s="26" t="inlineStr">
         <is>
           <t>Real</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C56" s="27" t="inlineStr">
         <is>
           <t>Real Estate Brokerage</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" s="26" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="E56" s="4" t="n">
+      <c r="E56" s="26" t="n">
         <v>1300000000</v>
       </c>
-      <c r="F56" s="4" t="n">
+      <c r="F56" s="26" t="n">
         <v>69600000</v>
       </c>
+      <c r="G56" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H56" s="23" t="inlineStr">
+        <is>
+          <t>Acquired The Solutions Group (Melbourne, FL — 60+ agents, $300M annual volume) to grow Space Coast/Central FL</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B57" s="26" t="inlineStr">
         <is>
           <t>GHR Healthcare</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C57" s="27" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="26" t="inlineStr">
         <is>
           <t>Blue Bell, PA</t>
         </is>
       </c>
-      <c r="E57" s="4" t="n">
+      <c r="E57" s="26" t="n">
         <v>1300000000</v>
       </c>
-      <c r="F57" s="4" t="n">
+      <c r="F57" s="26" t="n">
         <v>81400000</v>
+      </c>
+      <c r="G57" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H57" s="23" t="inlineStr">
+        <is>
+          <t>Tampa is 1 of only 5 GHR offices; acquired Meleeo (Tampa, FL)</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -2608,48 +3147,58 @@
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" s="26" t="inlineStr">
         <is>
           <t>Prime Communications</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" s="27" t="inlineStr">
         <is>
           <t>Telecommunications</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D59" s="26" t="inlineStr">
         <is>
           <t>Sugar Land, TX</t>
         </is>
       </c>
-      <c r="E59" s="4" t="n">
+      <c r="E59" s="26" t="n">
         <v>1200000000</v>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="F59" s="26" t="n">
         <v>146200000</v>
       </c>
+      <c r="G59" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H59" s="23" t="inlineStr">
+        <is>
+          <t>2,000+ AT&amp;T Authorized Retailer stores nationwide — scores in FL given state size</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="B60" s="14" t="inlineStr">
+      <c r="B60" s="19" t="inlineStr">
         <is>
           <t>Westgate Resorts</t>
         </is>
       </c>
-      <c r="C60" s="15" t="inlineStr">
+      <c r="C60" s="20" t="inlineStr">
         <is>
           <t>Hotels &amp; Resorts</t>
         </is>
       </c>
-      <c r="D60" s="14" t="inlineStr">
+      <c r="D60" s="19" t="inlineStr">
         <is>
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="E60" s="14" t="n">
+      <c r="E60" s="19" t="n">
         <v>1200000000</v>
       </c>
-      <c r="F60" s="14" t="n">
+      <c r="F60" s="19" t="n">
         <v>96000000</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
@@ -2657,56 +3206,76 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H60" s="13" t="inlineStr">
+      <c r="H60" s="18" t="inlineStr">
         <is>
           <t>HQ in Orlando, FL</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B61" s="26" t="inlineStr">
         <is>
           <t>Dal-Tile LLC</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="27" t="inlineStr">
         <is>
           <t>Wholesale</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D61" s="26" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
       </c>
-      <c r="E61" s="4" t="n">
+      <c r="E61" s="26" t="n">
         <v>1200000000</v>
       </c>
-      <c r="F61" s="4" t="n">
+      <c r="F61" s="26" t="n">
         <v>89000000</v>
       </c>
+      <c r="G61" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H61" s="23" t="inlineStr">
+        <is>
+          <t>Tampa was site of Dal-Tile's first Sales Service Center (1955); 300+ company-owned SSCs incl. FL</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" s="21" t="inlineStr">
         <is>
           <t>NES Fircroft</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C62" s="22" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D62" s="21" t="inlineStr">
         <is>
           <t>Altrincham, United Kingdom</t>
         </is>
       </c>
-      <c r="E62" s="2" t="n">
+      <c r="E62" s="21" t="n">
         <v>1100000000</v>
       </c>
-      <c r="F62" s="2" t="n">
+      <c r="F62" s="21" t="n">
         <v>83700000</v>
+      </c>
+      <c r="G62" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H62" s="23" t="inlineStr">
+        <is>
+          <t>Orlando office dedicated to Power &amp; Renewables</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -2733,25 +3302,25 @@
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="14" t="inlineStr">
+      <c r="B64" s="19" t="inlineStr">
         <is>
           <t>Power Design, Inc.</t>
         </is>
       </c>
-      <c r="C64" s="15" t="inlineStr">
+      <c r="C64" s="20" t="inlineStr">
         <is>
           <t>Construction &amp; Engineering</t>
         </is>
       </c>
-      <c r="D64" s="14" t="inlineStr">
+      <c r="D64" s="19" t="inlineStr">
         <is>
           <t>St. Petersburg, FL</t>
         </is>
       </c>
-      <c r="E64" s="14" t="n">
+      <c r="E64" s="19" t="n">
         <v>1100000000</v>
       </c>
-      <c r="F64" s="14" t="n">
+      <c r="F64" s="19" t="n">
         <v>52000000</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
@@ -2759,55 +3328,65 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H64" s="13" t="inlineStr">
+      <c r="H64" s="18" t="inlineStr">
         <is>
           <t>HQ in St. Petersburg, FL</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" s="24" t="inlineStr">
         <is>
           <t>Rexel USA</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C65" s="25" t="inlineStr">
         <is>
           <t>Home Appliances</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D65" s="24" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
       </c>
-      <c r="E65" s="2" t="n">
+      <c r="E65" s="24" t="n">
         <v>1100000000</v>
       </c>
-      <c r="F65" s="2" t="n">
+      <c r="F65" s="24" t="n">
         <v>87400000</v>
       </c>
+      <c r="G65" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H65" s="18" t="inlineStr">
+        <is>
+          <t>8+ FL branches incl. 150k sqft Orlando DC; Orlando branch, Tampa, Daytona, Pinellas Park, Lakeland, Sarasota, Miami, Hollywood/Ft. Lauderdale</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="B66" s="14" t="inlineStr">
+      <c r="B66" s="19" t="inlineStr">
         <is>
           <t>AV</t>
         </is>
       </c>
-      <c r="C66" s="15" t="inlineStr">
+      <c r="C66" s="20" t="inlineStr">
         <is>
           <t>Aerospace &amp; Defense</t>
         </is>
       </c>
-      <c r="D66" s="14" t="inlineStr">
+      <c r="D66" s="19" t="inlineStr">
         <is>
           <t>Sunrise, FL</t>
         </is>
       </c>
-      <c r="E66" s="14" t="n">
+      <c r="E66" s="19" t="n">
         <v>1000000000</v>
       </c>
-      <c r="F66" s="14" t="n">
+      <c r="F66" s="19" t="n">
         <v>28300000</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
@@ -2815,32 +3394,32 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H66" s="13" t="inlineStr">
+      <c r="H66" s="18" t="inlineStr">
         <is>
           <t>HQ in Sunrise, FL</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="14" t="inlineStr">
+      <c r="B67" s="19" t="inlineStr">
         <is>
           <t>Office Depot</t>
         </is>
       </c>
-      <c r="C67" s="15" t="inlineStr">
+      <c r="C67" s="20" t="inlineStr">
         <is>
           <t>Office Supplies &amp; Equipment</t>
         </is>
       </c>
-      <c r="D67" s="14" t="inlineStr">
+      <c r="D67" s="19" t="inlineStr">
         <is>
           <t>Boca Raton, FL</t>
         </is>
       </c>
-      <c r="E67" s="14" t="n">
+      <c r="E67" s="19" t="n">
         <v>989600000</v>
       </c>
-      <c r="F67" s="14" t="n">
+      <c r="F67" s="19" t="n">
         <v>54400000</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
@@ -2848,7 +3427,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H67" s="13" t="inlineStr">
+      <c r="H67" s="18" t="inlineStr">
         <is>
           <t>HQ in Boca Raton, FL</t>
         </is>
@@ -2878,164 +3457,234 @@
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B69" s="24" t="inlineStr">
         <is>
           <t>Langan Engineering &amp; Environmental Services</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C69" s="25" t="inlineStr">
         <is>
           <t>Construction &amp; Engineering</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D69" s="24" t="inlineStr">
         <is>
           <t>Parsippany, NJ</t>
         </is>
       </c>
-      <c r="E69" s="2" t="n">
+      <c r="E69" s="24" t="n">
         <v>869400000</v>
       </c>
-      <c r="F69" s="2" t="n">
+      <c r="F69" s="24" t="n">
         <v>60800000</v>
       </c>
+      <c r="G69" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H69" s="18" t="inlineStr">
+        <is>
+          <t>7 FL offices: Miami, Orlando, Fort Lauderdale, West Palm Beach, Tampa, Miami Lakes (Tampa office alone 25+ professionals)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="B70" s="4" t="inlineStr">
+      <c r="B70" s="19" t="inlineStr">
         <is>
           <t>AnnieMac Home Mortgage</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C70" s="20" t="inlineStr">
         <is>
           <t>Consumer Finance</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D70" s="19" t="inlineStr">
         <is>
           <t>Mount Laurel, NJ</t>
         </is>
       </c>
-      <c r="E70" s="4" t="n">
+      <c r="E70" s="19" t="n">
         <v>865100000</v>
       </c>
-      <c r="F70" s="4" t="n">
+      <c r="F70" s="19" t="n">
         <v>84800000</v>
       </c>
+      <c r="G70" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H70" s="18" t="inlineStr">
+        <is>
+          <t>Acquired Florida Funding; FL branches in Apollo Beach, Bartow, Crawfordville, New Smyrna Beach</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B71" s="26" t="inlineStr">
         <is>
           <t>Afni, Inc.</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C71" s="27" t="inlineStr">
         <is>
           <t>Consulting &amp; Outsourcing</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="D71" s="26" t="inlineStr">
         <is>
           <t>Bloomington, IL</t>
         </is>
       </c>
-      <c r="E71" s="4" t="n">
+      <c r="E71" s="26" t="n">
         <v>809000000</v>
       </c>
-      <c r="F71" s="4" t="n">
+      <c r="F71" s="26" t="n">
         <v>67200000</v>
       </c>
+      <c r="G71" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H71" s="23" t="inlineStr">
+        <is>
+          <t>FL is 1 of 7 listed Afni US operations states; FL contact center confirmed</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="B72" s="4" t="inlineStr">
+      <c r="B72" s="19" t="inlineStr">
         <is>
           <t>Informa Markets</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C72" s="20" t="inlineStr">
         <is>
           <t>Event Management Services</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="D72" s="19" t="inlineStr">
         <is>
           <t>London, United Kingdom</t>
         </is>
       </c>
-      <c r="E72" s="4" t="n">
+      <c r="E72" s="19" t="n">
         <v>759600000</v>
       </c>
-      <c r="F72" s="4" t="n">
+      <c r="F72" s="19" t="n">
         <v>60500000</v>
       </c>
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H72" s="18" t="inlineStr">
+        <is>
+          <t>Dedicated South Florida Ventures division — owns Fort Lauderdale Boat Show, Miami Boat Show, St. Pete Power &amp; Sailboat Show, Art Miami, Art Wynwood, FIME Miami, AMWC Miami</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B73" s="24" t="inlineStr">
         <is>
           <t>Vaco</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C73" s="25" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D73" s="24" t="inlineStr">
         <is>
           <t>Brentwood, TN</t>
         </is>
       </c>
-      <c r="E73" s="2" t="n">
+      <c r="E73" s="24" t="n">
         <v>753600000</v>
       </c>
-      <c r="F73" s="2" t="n">
+      <c r="F73" s="24" t="n">
         <v>60100000</v>
       </c>
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H73" s="18" t="inlineStr">
+        <is>
+          <t>4-5 FL offices: Miami (South FL), Tampa, Orlando (Maitland), Jacksonville, West Palm Beach + prior FL finance/IT acquisition</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="B74" s="4" t="inlineStr">
+      <c r="B74" s="19" t="inlineStr">
         <is>
           <t>Genesis Health Clubs</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C74" s="20" t="inlineStr">
         <is>
           <t>Health &amp; Wellness Services</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="D74" s="19" t="inlineStr">
         <is>
           <t>Wichita, KS</t>
         </is>
       </c>
-      <c r="E74" s="4" t="n">
+      <c r="E74" s="19" t="n">
         <v>740900000</v>
       </c>
-      <c r="F74" s="4" t="n">
+      <c r="F74" s="19" t="n">
         <v>76800000</v>
       </c>
+      <c r="G74" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H74" s="18" t="inlineStr">
+        <is>
+          <t>2022 FL entry via acquisition; exclusive fitness provider in The Villages (Brownwood + Spanish Springs) + Orlando Sportsplex</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B75" s="19" t="inlineStr">
         <is>
           <t>First Onsite Property Restoration</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C75" s="20" t="inlineStr">
         <is>
           <t>Construction &amp; Engineering</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D75" s="19" t="inlineStr">
         <is>
           <t>Englewood, CO</t>
         </is>
       </c>
-      <c r="E75" s="4" t="n">
+      <c r="E75" s="19" t="n">
         <v>726900000</v>
       </c>
-      <c r="F75" s="4" t="n">
+      <c r="F75" s="19" t="n">
         <v>63400000</v>
+      </c>
+      <c r="G75" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H75" s="18" t="inlineStr">
+        <is>
+          <t>Acquired Complete DKI (Pensacola/Tallahassee, 2021) — FL is a 'high-priority region' for hurricane/catastrophe response; statewide FL coverage</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -3062,48 +3711,58 @@
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B77" s="21" t="inlineStr">
         <is>
           <t>UICGS / Bowhead Family of Companies</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C77" s="22" t="inlineStr">
         <is>
           <t>IT Services</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D77" s="21" t="inlineStr">
         <is>
           <t>Springfield, VA</t>
         </is>
       </c>
-      <c r="E77" s="2" t="n">
+      <c r="E77" s="21" t="n">
         <v>710200000</v>
       </c>
-      <c r="F77" s="2" t="n">
+      <c r="F77" s="21" t="n">
         <v>57000000</v>
       </c>
+      <c r="G77" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H77" s="23" t="inlineStr">
+        <is>
+          <t>Dedicated Pensacola, FL office supporting Navy/DoD work</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="B78" s="14" t="inlineStr">
+      <c r="B78" s="19" t="inlineStr">
         <is>
           <t>DEX Imaging</t>
         </is>
       </c>
-      <c r="C78" s="15" t="inlineStr">
+      <c r="C78" s="20" t="inlineStr">
         <is>
           <t>Office Supplies &amp; Equipment</t>
         </is>
       </c>
-      <c r="D78" s="14" t="inlineStr">
+      <c r="D78" s="19" t="inlineStr">
         <is>
           <t>Tampa, FL</t>
         </is>
       </c>
-      <c r="E78" s="14" t="n">
+      <c r="E78" s="19" t="n">
         <v>704600000</v>
       </c>
-      <c r="F78" s="14" t="n">
+      <c r="F78" s="19" t="n">
         <v>64500000</v>
       </c>
       <c r="G78" s="12" t="inlineStr">
@@ -3111,102 +3770,142 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H78" s="13" t="inlineStr">
+      <c r="H78" s="18" t="inlineStr">
         <is>
           <t>HQ in Tampa, FL</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B79" s="26" t="inlineStr">
         <is>
           <t>Miracle-Ear, Inc.</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C79" s="27" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D79" s="26" t="inlineStr">
         <is>
           <t>Minneapolis, MN</t>
         </is>
       </c>
-      <c r="E79" s="4" t="n">
+      <c r="E79" s="26" t="n">
         <v>697200000</v>
       </c>
-      <c r="F79" s="4" t="n">
+      <c r="F79" s="26" t="n">
         <v>59500000</v>
       </c>
+      <c r="G79" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H79" s="23" t="inlineStr">
+        <is>
+          <t>Many FL franchise locations (Tampa, St. Pete, Orlando, Boca Raton, Palm Harbor, Melbourne) — FL is demographically critical for hearing aids</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B80" s="19" t="inlineStr">
         <is>
           <t>Montrose Environmental Group</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C80" s="20" t="inlineStr">
         <is>
           <t>Environmental Consulting</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D80" s="19" t="inlineStr">
         <is>
           <t>Little Rock, AR</t>
         </is>
       </c>
-      <c r="E80" s="4" t="n">
+      <c r="E80" s="19" t="n">
         <v>696400000</v>
       </c>
-      <c r="F80" s="4" t="n">
+      <c r="F80" s="19" t="n">
         <v>27900000</v>
       </c>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H80" s="18" t="inlineStr">
+        <is>
+          <t>Acquired Orlando-based MSE Group (FL HQ + 3 satellites, 2021) and Tampa-based FGS Group</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B81" s="24" t="inlineStr">
         <is>
           <t>CentiMark Corporation</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C81" s="25" t="inlineStr">
         <is>
           <t>Construction &amp; Engineering</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D81" s="24" t="inlineStr">
         <is>
           <t>Canonsburg, PA</t>
         </is>
       </c>
-      <c r="E81" s="2" t="n">
+      <c r="E81" s="24" t="n">
         <v>691700000</v>
       </c>
-      <c r="F81" s="2" t="n">
+      <c r="F81" s="24" t="n">
         <v>48400000</v>
       </c>
+      <c r="G81" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H81" s="18" t="inlineStr">
+        <is>
+          <t>5 dedicated FL offices: Tampa/Lakeland, Pompano Beach, Orlando, Jacksonville (10 crews), Pensacola</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="B82" s="4" t="inlineStr">
+      <c r="B82" s="26" t="inlineStr">
         <is>
           <t>Aston Carter</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C82" s="27" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="D82" s="26" t="inlineStr">
         <is>
           <t>London, United Kingdom</t>
         </is>
       </c>
-      <c r="E82" s="4" t="n">
+      <c r="E82" s="26" t="n">
         <v>635900000</v>
       </c>
-      <c r="F82" s="4" t="n">
+      <c r="F82" s="26" t="n">
         <v>50600000</v>
+      </c>
+      <c r="G82" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H82" s="23" t="inlineStr">
+        <is>
+          <t>2 FL offices (Miami/Doral and Tampa); Tampa earned 2025 Best of Staffing</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -3233,26 +3932,36 @@
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B84" s="19" t="inlineStr">
         <is>
           <t>Hunt Companies, Inc</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C84" s="20" t="inlineStr">
         <is>
           <t>Real Estate Development</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D84" s="19" t="inlineStr">
         <is>
           <t>El Paso, TX</t>
         </is>
       </c>
-      <c r="E84" s="4" t="n">
+      <c r="E84" s="19" t="n">
         <v>617300000</v>
       </c>
-      <c r="F84" s="4" t="n">
+      <c r="F84" s="19" t="n">
         <v>42100000</v>
+      </c>
+      <c r="G84" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H84" s="18" t="inlineStr">
+        <is>
+          <t>Hunt Real Estate Services in Tampa (5100 W Kennedy Blvd); Hunt Realty Group covers Tampa-Punta Gorda; owns/manages Patrick Family Housing (616 homes at Patrick Space Force Base, FL)</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -3279,26 +3988,36 @@
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="4" t="inlineStr">
+      <c r="B86" s="19" t="inlineStr">
         <is>
           <t>ECS Group of Companies</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C86" s="20" t="inlineStr">
         <is>
           <t>Consulting &amp; Outsourcing</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="D86" s="19" t="inlineStr">
         <is>
           <t>Chantilly, VA</t>
         </is>
       </c>
-      <c r="E86" s="4" t="n">
+      <c r="E86" s="19" t="n">
         <v>612100000</v>
       </c>
-      <c r="F86" s="4" t="n">
+      <c r="F86" s="19" t="n">
         <v>49000000</v>
+      </c>
+      <c r="G86" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H86" s="18" t="inlineStr">
+        <is>
+          <t>Dedicated subsidiary ECS Florida, LLC HQ in Orlando</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -3348,95 +4067,135 @@
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="4" t="inlineStr">
+      <c r="B89" s="19" t="inlineStr">
         <is>
           <t>Window World</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C89" s="20" t="inlineStr">
         <is>
           <t>Building Products</t>
         </is>
       </c>
-      <c r="D89" s="4" t="inlineStr">
+      <c r="D89" s="19" t="inlineStr">
         <is>
           <t>North Wilkesboro, NC</t>
         </is>
       </c>
-      <c r="E89" s="4" t="n">
+      <c r="E89" s="19" t="n">
         <v>600000000</v>
       </c>
-      <c r="F89" s="4" t="n">
+      <c r="F89" s="19" t="n">
         <v>42000000</v>
       </c>
+      <c r="G89" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H89" s="18" t="inlineStr">
+        <is>
+          <t>13 FL franchise locations from Jacksonville to West Palm Beach</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="B90" s="4" t="inlineStr">
+      <c r="B90" s="26" t="inlineStr">
         <is>
           <t>Integrated Power Services</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C90" s="27" t="inlineStr">
         <is>
           <t>Industrial Machinery</t>
         </is>
       </c>
-      <c r="D90" s="4" t="inlineStr">
+      <c r="D90" s="26" t="inlineStr">
         <is>
           <t>Greenville, SC</t>
         </is>
       </c>
-      <c r="E90" s="4" t="n">
+      <c r="E90" s="26" t="n">
         <v>568100000</v>
       </c>
-      <c r="F90" s="4" t="n">
+      <c r="F90" s="26" t="n">
         <v>39800000</v>
       </c>
+      <c r="G90" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H90" s="23" t="inlineStr">
+        <is>
+          <t>2 FL facilities: Riverview (Tampa area) + TAW Lake City Repair &amp; Service Center</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="B91" s="4" t="inlineStr">
+      <c r="B91" s="26" t="inlineStr">
         <is>
           <t>The Planet Group</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C91" s="27" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="D91" s="26" t="inlineStr">
         <is>
           <t>Deerfield, IL</t>
         </is>
       </c>
-      <c r="E91" s="4" t="n">
+      <c r="E91" s="26" t="n">
         <v>538300000</v>
       </c>
-      <c r="F91" s="4" t="n">
+      <c r="F91" s="26" t="n">
         <v>44800000</v>
       </c>
+      <c r="G91" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H91" s="23" t="inlineStr">
+        <is>
+          <t>Dedicated FL staffing practice covering Miami, Orlando, Tampa, Jacksonville with FL landing page</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B92" s="24" t="inlineStr">
         <is>
           <t>Choice Home Warranty</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C92" s="25" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="D92" s="24" t="inlineStr">
         <is>
           <t>Edison, NJ</t>
         </is>
       </c>
-      <c r="E92" s="2" t="n">
+      <c r="E92" s="24" t="n">
         <v>537600000</v>
       </c>
-      <c r="F92" s="2" t="n">
+      <c r="F92" s="24" t="n">
         <v>45500000</v>
+      </c>
+      <c r="G92" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H92" s="18" t="inlineStr">
+        <is>
+          <t>FL is among their largest markets — heavy FL marketing + dedicated FL landing page; FL AG received 50 complaints in one year (massive customer base)</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -3463,94 +4222,124 @@
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B94" s="19" t="inlineStr">
         <is>
           <t>Noatum Logistics</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
+      <c r="C94" s="20" t="inlineStr">
         <is>
           <t>Intermodal and Logistics Services</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
+      <c r="D94" s="19" t="inlineStr">
         <is>
           <t>Madrid, Spain</t>
         </is>
       </c>
-      <c r="E94" s="4" t="n">
+      <c r="E94" s="19" t="n">
         <v>526700000</v>
       </c>
-      <c r="F94" s="4" t="n">
+      <c r="F94" s="19" t="n">
         <v>43600000</v>
       </c>
+      <c r="G94" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H94" s="18" t="inlineStr">
+        <is>
+          <t>Two Doral, FL facilities (freight forwarding/warehouse + cold/frozen storage); Miami/Doral is a flagship US hub</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="B95" s="4" t="inlineStr">
+      <c r="B95" s="19" t="inlineStr">
         <is>
           <t>Sunstates Security</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C95" s="20" t="inlineStr">
         <is>
           <t>Private Security Services</t>
         </is>
       </c>
-      <c r="D95" s="4" t="inlineStr">
+      <c r="D95" s="19" t="inlineStr">
         <is>
           <t>Raleigh, NC</t>
         </is>
       </c>
-      <c r="E95" s="4" t="n">
+      <c r="E95" s="19" t="n">
         <v>515000000</v>
       </c>
-      <c r="F95" s="4" t="n">
+      <c r="F95" s="19" t="n">
         <v>42600000</v>
       </c>
+      <c r="G95" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H95" s="18" t="inlineStr">
+        <is>
+          <t>Multiple FL offices: Boca Raton, Boynton Beach, Fort Lauderdale, Miami, Orlando, Riviera Beach (regional structure with Orlando + South FL hubs)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="B96" s="4" t="inlineStr">
+      <c r="B96" s="19" t="inlineStr">
         <is>
           <t>FreshPoint, Inc.</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
+      <c r="C96" s="20" t="inlineStr">
         <is>
           <t>Food &amp; Beverage Products</t>
         </is>
       </c>
-      <c r="D96" s="4" t="inlineStr">
+      <c r="D96" s="19" t="inlineStr">
         <is>
           <t>Houston, TX</t>
         </is>
       </c>
-      <c r="E96" s="4" t="n">
+      <c r="E96" s="19" t="n">
         <v>510200000</v>
       </c>
-      <c r="F96" s="4" t="n">
+      <c r="F96" s="19" t="n">
         <v>50800000</v>
       </c>
+      <c r="G96" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H96" s="18" t="inlineStr">
+        <is>
+          <t>3 dedicated FL operating companies: FreshPoint Central Florida (Orlando), South Florida (Pompano Beach), West Coast Florida (Tampa)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="B97" s="14" t="inlineStr">
+      <c r="B97" s="19" t="inlineStr">
         <is>
           <t>Optavise</t>
         </is>
       </c>
-      <c r="C97" s="15" t="inlineStr">
+      <c r="C97" s="20" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D97" s="14" t="inlineStr">
+      <c r="D97" s="19" t="inlineStr">
         <is>
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="E97" s="14" t="n">
+      <c r="E97" s="19" t="n">
         <v>510000000</v>
       </c>
-      <c r="F97" s="14" t="n">
+      <c r="F97" s="19" t="n">
         <v>43200000</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
@@ -3558,125 +4347,175 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H97" s="13" t="inlineStr">
+      <c r="H97" s="18" t="inlineStr">
         <is>
           <t>HQ in Orlando, FL</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="4" t="inlineStr">
+      <c r="B98" s="19" t="inlineStr">
         <is>
           <t>Maxim Crane Works, LP</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
+      <c r="C98" s="20" t="inlineStr">
         <is>
           <t>Construction &amp; Engineering</t>
         </is>
       </c>
-      <c r="D98" s="4" t="inlineStr">
+      <c r="D98" s="19" t="inlineStr">
         <is>
           <t>Wilder, KY</t>
         </is>
       </c>
-      <c r="E98" s="4" t="n">
+      <c r="E98" s="19" t="n">
         <v>494100000</v>
       </c>
-      <c r="F98" s="4" t="n">
+      <c r="F98" s="19" t="n">
         <v>26500000</v>
       </c>
+      <c r="G98" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H98" s="18" t="inlineStr">
+        <is>
+          <t>5 FL branches: Fort Lauderdale, Pompano Beach, Orlando, Davenport, Tampa — one of heaviest state concentrations</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B99" s="24" t="inlineStr">
         <is>
           <t>Salas O'Brien</t>
         </is>
       </c>
-      <c r="C99" s="3" t="inlineStr">
+      <c r="C99" s="25" t="inlineStr">
         <is>
           <t>Architectural &amp; Engineering Services</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="D99" s="24" t="inlineStr">
         <is>
           <t>Irvine, CA</t>
         </is>
       </c>
-      <c r="E99" s="2" t="n">
+      <c r="E99" s="24" t="n">
         <v>492900000</v>
       </c>
-      <c r="F99" s="2" t="n">
+      <c r="F99" s="24" t="n">
         <v>23200000</v>
       </c>
+      <c r="G99" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H99" s="18" t="inlineStr">
+        <is>
+          <t>Acquired Nelson Engineering (FL, 2022) + Moisture Intrusion Solutions (Daytona Beach); dedicated FL offices page</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="B100" s="4" t="inlineStr">
+      <c r="B100" s="19" t="inlineStr">
         <is>
           <t>Emser Tile</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
+      <c r="C100" s="20" t="inlineStr">
         <is>
           <t>Building Products</t>
         </is>
       </c>
-      <c r="D100" s="4" t="inlineStr">
+      <c r="D100" s="19" t="inlineStr">
         <is>
           <t>Los Angeles, CA</t>
         </is>
       </c>
-      <c r="E100" s="4" t="n">
+      <c r="E100" s="19" t="n">
         <v>485300000</v>
       </c>
-      <c r="F100" s="4" t="n">
+      <c r="F100" s="19" t="n">
         <v>28100000</v>
       </c>
+      <c r="G100" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H100" s="18" t="inlineStr">
+        <is>
+          <t>6 FL showroom/service centers + 220k sqft Coral Springs DC (1 of only 4 in North America); explicitly targeted as a major growth market</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="B101" s="4" t="inlineStr">
+      <c r="B101" s="19" t="inlineStr">
         <is>
           <t>D1 TRAINING</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
+      <c r="C101" s="20" t="inlineStr">
         <is>
           <t>Health &amp; Wellness Services</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr">
+      <c r="D101" s="19" t="inlineStr">
         <is>
           <t>Franklin, TN</t>
         </is>
       </c>
-      <c r="E101" s="4" t="n">
+      <c r="E101" s="19" t="n">
         <v>479800000</v>
       </c>
-      <c r="F101" s="4" t="n">
+      <c r="F101" s="19" t="n">
         <v>33100000</v>
       </c>
+      <c r="G101" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H101" s="18" t="inlineStr">
+        <is>
+          <t>Multiple FL franchises: Lake Mary, Downtown Orlando, SE Orlando, Deerfield Beach, Fort Myers</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="B102" s="4" t="inlineStr">
+      <c r="B102" s="19" t="inlineStr">
         <is>
           <t>Bunzl Distribution NA</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
+      <c r="C102" s="20" t="inlineStr">
         <is>
           <t>Intermodal and Logistics Services</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
+      <c r="D102" s="19" t="inlineStr">
         <is>
           <t>St. Louis, MO</t>
         </is>
       </c>
-      <c r="E102" s="4" t="n">
+      <c r="E102" s="19" t="n">
         <v>460100000</v>
       </c>
-      <c r="F102" s="4" t="n">
+      <c r="F102" s="19" t="n">
         <v>30600000</v>
+      </c>
+      <c r="G102" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H102" s="18" t="inlineStr">
+        <is>
+          <t>Multiple FL warehouses: Tampa (2), Miramar, Boynton Beach (Monte Southeast), Lakeland (Monte Central FL)</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -3703,117 +4542,157 @@
       </c>
     </row>
     <row r="104">
-      <c r="B104" s="4" t="inlineStr">
+      <c r="B104" s="26" t="inlineStr">
         <is>
           <t>Floor Coverings International</t>
         </is>
       </c>
-      <c r="C104" s="5" t="inlineStr">
+      <c r="C104" s="27" t="inlineStr">
         <is>
           <t>Specialty Retail</t>
         </is>
       </c>
-      <c r="D104" s="4" t="inlineStr">
+      <c r="D104" s="26" t="inlineStr">
         <is>
           <t>Smyrna, GA</t>
         </is>
       </c>
-      <c r="E104" s="4" t="n">
+      <c r="E104" s="26" t="n">
         <v>448900000</v>
       </c>
-      <c r="F104" s="4" t="n">
+      <c r="F104" s="26" t="n">
         <v>35700000</v>
       </c>
+      <c r="G104" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H104" s="23" t="inlineStr">
+        <is>
+          <t>Multiple FL franchises: Pensacola/Panhandle, Weston, Winter Garden, Temple Terrace, St. Augustine + resales in Jacksonville/Boynton Beach</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="B105" s="4" t="inlineStr">
+      <c r="B105" s="19" t="inlineStr">
         <is>
           <t>SRM Concrete</t>
         </is>
       </c>
-      <c r="C105" s="5" t="inlineStr">
+      <c r="C105" s="20" t="inlineStr">
         <is>
           <t>Construction &amp; Engineering</t>
         </is>
       </c>
-      <c r="D105" s="4" t="inlineStr">
+      <c r="D105" s="19" t="inlineStr">
         <is>
           <t>Smyrna, TN</t>
         </is>
       </c>
-      <c r="E105" s="4" t="n">
+      <c r="E105" s="19" t="n">
         <v>443900000</v>
       </c>
-      <c r="F105" s="4" t="n">
+      <c r="F105" s="19" t="n">
         <v>23800000</v>
       </c>
+      <c r="G105" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H105" s="18" t="inlineStr">
+        <is>
+          <t>Entered FL via 2018 KMR Concrete (Bartow) acquisition; 5 plants from Argos USA; Environmental Concrete &amp; Materials (Fort Myers); Young Trucking (largest bulk cement distributor in SW FL); plants in Haines City, Lakeland, Mulberry, Bartow, Fort Myers</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B106" s="21" t="inlineStr">
         <is>
           <t>Informa Connect</t>
         </is>
       </c>
-      <c r="C106" s="3" t="inlineStr">
+      <c r="C106" s="22" t="inlineStr">
         <is>
           <t>IT Services</t>
         </is>
       </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="D106" s="21" t="inlineStr">
         <is>
           <t>London, United Kingdom</t>
         </is>
       </c>
-      <c r="E106" s="2" t="n">
+      <c r="E106" s="21" t="n">
         <v>412900000</v>
       </c>
-      <c r="F106" s="2" t="n">
+      <c r="F106" s="21" t="n">
         <v>28600000</v>
       </c>
+      <c r="G106" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H106" s="23" t="inlineStr">
+        <is>
+          <t>Hosts flagship events in FL annually (Connect Marketplace in Tampa; Enterprise Connect at Gaylord Palms)</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="B107" s="4" t="inlineStr">
+      <c r="B107" s="19" t="inlineStr">
         <is>
           <t>Nesco Resource</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
+      <c r="C107" s="20" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D107" s="4" t="inlineStr">
+      <c r="D107" s="19" t="inlineStr">
         <is>
           <t>Mayfield Heights, OH</t>
         </is>
       </c>
-      <c r="E107" s="4" t="n">
+      <c r="E107" s="19" t="n">
         <v>412700000</v>
       </c>
-      <c r="F107" s="4" t="n">
+      <c r="F107" s="19" t="n">
         <v>27400000</v>
       </c>
+      <c r="G107" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H107" s="18" t="inlineStr">
+        <is>
+          <t>8+ FL branches: Orlando, Lake Mary, Casselberry, Tampa, West Tampa, Temple Terrace, Clearwater, Lakeland, Pinellas Park, St. Pete</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="B108" s="14" t="inlineStr">
+      <c r="B108" s="19" t="inlineStr">
         <is>
           <t>Baker Distributing Company</t>
         </is>
       </c>
-      <c r="C108" s="15" t="inlineStr">
+      <c r="C108" s="20" t="inlineStr">
         <is>
           <t>Wholesale</t>
         </is>
       </c>
-      <c r="D108" s="14" t="inlineStr">
+      <c r="D108" s="19" t="inlineStr">
         <is>
           <t>Jacksonville, FL</t>
         </is>
       </c>
-      <c r="E108" s="14" t="n">
+      <c r="E108" s="19" t="n">
         <v>386900000</v>
       </c>
-      <c r="F108" s="14" t="n">
+      <c r="F108" s="19" t="n">
         <v>22400000</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
@@ -3821,33 +4700,43 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H108" s="13" t="inlineStr">
+      <c r="H108" s="18" t="inlineStr">
         <is>
           <t>HQ in Jacksonville, FL</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="B109" s="4" t="inlineStr">
+      <c r="B109" s="19" t="inlineStr">
         <is>
           <t>Ultimate Staffing</t>
         </is>
       </c>
-      <c r="C109" s="5" t="inlineStr">
+      <c r="C109" s="20" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr">
+      <c r="D109" s="19" t="inlineStr">
         <is>
           <t>Orange, CA</t>
         </is>
       </c>
-      <c r="E109" s="4" t="n">
+      <c r="E109" s="19" t="n">
         <v>375000000</v>
       </c>
-      <c r="F109" s="4" t="n">
+      <c r="F109" s="19" t="n">
         <v>28000000</v>
+      </c>
+      <c r="G109" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H109" s="18" t="inlineStr">
+        <is>
+          <t>5+ FL offices: Orlando, Fort Lauderdale, West Palm Beach, Boca Raton, Oakland Park/Lauderdale Lakes</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -3874,186 +4763,256 @@
       </c>
     </row>
     <row r="111">
-      <c r="B111" s="4" t="inlineStr">
+      <c r="B111" s="19" t="inlineStr">
         <is>
           <t>Moneycorp</t>
         </is>
       </c>
-      <c r="C111" s="5" t="inlineStr">
+      <c r="C111" s="20" t="inlineStr">
         <is>
           <t>Accounting &amp; Financial Services</t>
         </is>
       </c>
-      <c r="D111" s="4" t="inlineStr">
+      <c r="D111" s="19" t="inlineStr">
         <is>
           <t>London, United Kingdom</t>
         </is>
       </c>
-      <c r="E111" s="4" t="n">
+      <c r="E111" s="19" t="n">
         <v>344100000</v>
       </c>
-      <c r="F111" s="4" t="n">
+      <c r="F111" s="19" t="n">
         <v>21800000</v>
       </c>
+      <c r="G111" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H111" s="18" t="inlineStr">
+        <is>
+          <t>US HQ in Orlando, FL (7380 Sand Lake Road) — primary operational hub for US business</t>
+        </is>
+      </c>
     </row>
     <row r="112">
-      <c r="B112" s="4" t="inlineStr">
+      <c r="B112" s="26" t="inlineStr">
         <is>
           <t>Rakuten Advertising</t>
         </is>
       </c>
-      <c r="C112" s="5" t="inlineStr">
+      <c r="C112" s="27" t="inlineStr">
         <is>
           <t>Internet of Things (IoT)</t>
         </is>
       </c>
-      <c r="D112" s="4" t="inlineStr">
+      <c r="D112" s="26" t="inlineStr">
         <is>
           <t>San Mateo, CA</t>
         </is>
       </c>
-      <c r="E112" s="4" t="n">
+      <c r="E112" s="26" t="n">
         <v>328000000</v>
       </c>
-      <c r="F112" s="4" t="n">
+      <c r="F112" s="26" t="n">
         <v>22400000</v>
       </c>
+      <c r="G112" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H112" s="23" t="inlineStr">
+        <is>
+          <t>Tampa office (100 S Ashley Dr)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B113" s="24" t="inlineStr">
         <is>
           <t>System One</t>
         </is>
       </c>
-      <c r="C113" s="3" t="inlineStr">
+      <c r="C113" s="25" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="D113" s="24" t="inlineStr">
         <is>
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="E113" s="2" t="n">
+      <c r="E113" s="24" t="n">
         <v>303800000</v>
       </c>
-      <c r="F113" s="2" t="n">
+      <c r="F113" s="24" t="n">
         <v>20200000</v>
       </c>
+      <c r="G113" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H113" s="18" t="inlineStr">
+        <is>
+          <t>3 FL offices: Orlando, Tampa, Miami</t>
+        </is>
+      </c>
     </row>
     <row r="114">
-      <c r="B114" s="4" t="inlineStr">
+      <c r="B114" s="19" t="inlineStr">
         <is>
           <t>Erie Home</t>
         </is>
       </c>
-      <c r="C114" s="5" t="inlineStr">
+      <c r="C114" s="20" t="inlineStr">
         <is>
           <t>Construction &amp; Engineering</t>
         </is>
       </c>
-      <c r="D114" s="4" t="inlineStr">
+      <c r="D114" s="19" t="inlineStr">
         <is>
           <t>Toledo, OH</t>
         </is>
       </c>
-      <c r="E114" s="4" t="n">
+      <c r="E114" s="19" t="n">
         <v>287900000</v>
       </c>
-      <c r="F114" s="4" t="n">
+      <c r="F114" s="19" t="n">
         <v>20700000</v>
       </c>
+      <c r="G114" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H114" s="18" t="inlineStr">
+        <is>
+          <t>6+ FL roofing branches: Jacksonville, Orlando, Westchase (Tampa), Palm Bay, Sarasota, Tallahassee — hurricane-driven roofing demand</t>
+        </is>
+      </c>
     </row>
     <row r="115">
-      <c r="B115" s="4" t="inlineStr">
+      <c r="B115" s="26" t="inlineStr">
         <is>
           <t>Reliable Automatic Sprinkler Co., Inc.</t>
         </is>
       </c>
-      <c r="C115" s="5" t="inlineStr">
+      <c r="C115" s="27" t="inlineStr">
         <is>
           <t>Wholesale</t>
         </is>
       </c>
-      <c r="D115" s="4" t="inlineStr">
+      <c r="D115" s="26" t="inlineStr">
         <is>
           <t>Liberty, SC</t>
         </is>
       </c>
-      <c r="E115" s="4" t="n">
+      <c r="E115" s="26" t="n">
         <v>275300000</v>
       </c>
-      <c r="F115" s="4" t="n">
+      <c r="F115" s="26" t="n">
         <v>16000000</v>
       </c>
+      <c r="G115" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H115" s="23" t="inlineStr">
+        <is>
+          <t>South FL distribution facility in Miramar serving SE FL, PR, Caribbean, South America + Orlando location</t>
+        </is>
+      </c>
     </row>
     <row r="116">
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B116" s="24" t="inlineStr">
         <is>
           <t>RemX | The Workforce Experts</t>
         </is>
       </c>
-      <c r="C116" s="3" t="inlineStr">
+      <c r="C116" s="25" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="D116" s="24" t="inlineStr">
         <is>
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="E116" s="2" t="n">
+      <c r="E116" s="24" t="n">
         <v>275100000</v>
       </c>
-      <c r="F116" s="2" t="n">
+      <c r="F116" s="24" t="n">
         <v>18300000</v>
       </c>
+      <c r="G116" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H116" s="18" t="inlineStr">
+        <is>
+          <t>4 FL offices: Jacksonville, Doral/Miami, Orlando, Tampa; RemX Hub Orlando is a financial/professional services hub</t>
+        </is>
+      </c>
     </row>
     <row r="117">
-      <c r="B117" s="4" t="inlineStr">
+      <c r="B117" s="19" t="inlineStr">
         <is>
           <t>BGSF</t>
         </is>
       </c>
-      <c r="C117" s="5" t="inlineStr">
+      <c r="C117" s="20" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D117" s="4" t="inlineStr">
+      <c r="D117" s="19" t="inlineStr">
         <is>
           <t>Plano, TX</t>
         </is>
       </c>
-      <c r="E117" s="4" t="n">
+      <c r="E117" s="19" t="n">
         <v>272500000</v>
       </c>
-      <c r="F117" s="4" t="n">
+      <c r="F117" s="19" t="n">
         <v>17700000</v>
       </c>
+      <c r="G117" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H117" s="18" t="inlineStr">
+        <is>
+          <t>5 FL multifamily staffing markets: Orlando, Jacksonville, Tampa, Fort Lauderdale, Miami</t>
+        </is>
+      </c>
     </row>
     <row r="118">
-      <c r="B118" s="14" t="inlineStr">
+      <c r="B118" s="19" t="inlineStr">
         <is>
           <t>National Dentex Labs</t>
         </is>
       </c>
-      <c r="C118" s="15" t="inlineStr">
+      <c r="C118" s="20" t="inlineStr">
         <is>
           <t>Healthcare Facilities</t>
         </is>
       </c>
-      <c r="D118" s="14" t="inlineStr">
+      <c r="D118" s="19" t="inlineStr">
         <is>
           <t>Palm Beach Gardens, FL</t>
         </is>
       </c>
-      <c r="E118" s="14" t="n">
+      <c r="E118" s="19" t="n">
         <v>266899999</v>
       </c>
-      <c r="F118" s="14" t="n">
+      <c r="F118" s="19" t="n">
         <v>19600000</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
@@ -4061,56 +5020,76 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H118" s="13" t="inlineStr">
+      <c r="H118" s="18" t="inlineStr">
         <is>
           <t>HQ in Palm Beach Gardens, FL</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="B119" s="4" t="inlineStr">
+      <c r="B119" s="19" t="inlineStr">
         <is>
           <t>Metrie</t>
         </is>
       </c>
-      <c r="C119" s="5" t="inlineStr">
+      <c r="C119" s="20" t="inlineStr">
         <is>
           <t>Building Products</t>
         </is>
       </c>
-      <c r="D119" s="4" t="inlineStr">
+      <c r="D119" s="19" t="inlineStr">
         <is>
           <t>Vancouver, Canada</t>
         </is>
       </c>
-      <c r="E119" s="4" t="n">
+      <c r="E119" s="19" t="n">
         <v>266200000</v>
       </c>
-      <c r="F119" s="4" t="n">
+      <c r="F119" s="19" t="n">
         <v>15400000</v>
       </c>
+      <c r="G119" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H119" s="18" t="inlineStr">
+        <is>
+          <t>Orlando moulding DC; acquired Florida Made Door (Yulee, FL); explicit 'key market' for door expansion</t>
+        </is>
+      </c>
     </row>
     <row r="120">
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B120" s="24" t="inlineStr">
         <is>
           <t>Doeren Mayhew</t>
         </is>
       </c>
-      <c r="C120" s="3" t="inlineStr">
+      <c r="C120" s="25" t="inlineStr">
         <is>
           <t>Accounting &amp; Financial Services</t>
         </is>
       </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="D120" s="24" t="inlineStr">
         <is>
           <t>Troy, MI</t>
         </is>
       </c>
-      <c r="E120" s="2" t="n">
+      <c r="E120" s="24" t="n">
         <v>250600000</v>
       </c>
-      <c r="F120" s="2" t="n">
+      <c r="F120" s="24" t="n">
         <v>15900000</v>
+      </c>
+      <c r="G120" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H120" s="18" t="inlineStr">
+        <is>
+          <t>4+ FL offices via 2025-26 acquisitions: Miami, South Miami, Key Biscayne (Lancaster &amp; Reed), Orlando + Melbourne (Berman Hopkins), Parlade Schaefer Schortz</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -4137,26 +5116,36 @@
       </c>
     </row>
     <row r="122">
-      <c r="B122" s="4" t="inlineStr">
+      <c r="B122" s="19" t="inlineStr">
         <is>
           <t>Alaka`ina Foundation Family of Companies</t>
         </is>
       </c>
-      <c r="C122" s="5" t="inlineStr">
+      <c r="C122" s="20" t="inlineStr">
         <is>
           <t>Public Administration</t>
         </is>
       </c>
-      <c r="D122" s="4" t="inlineStr">
+      <c r="D122" s="19" t="inlineStr">
         <is>
           <t>Honolulu, HI</t>
         </is>
       </c>
-      <c r="E122" s="4" t="n">
+      <c r="E122" s="19" t="n">
         <v>241700000</v>
       </c>
-      <c r="F122" s="4" t="n">
+      <c r="F122" s="19" t="n">
         <v>4800000</v>
+      </c>
+      <c r="G122" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H122" s="18" t="inlineStr">
+        <is>
+          <t>Major Orlando office at 12565 Research Parkway with 500-1,000 employees</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -4183,26 +5172,36 @@
       </c>
     </row>
     <row r="124">
-      <c r="B124" s="4" t="inlineStr">
+      <c r="B124" s="26" t="inlineStr">
         <is>
           <t>Peoplelink Group</t>
         </is>
       </c>
-      <c r="C124" s="5" t="inlineStr">
+      <c r="C124" s="27" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D124" s="4" t="inlineStr">
+      <c r="D124" s="26" t="inlineStr">
         <is>
           <t>South Bend, IN</t>
         </is>
       </c>
-      <c r="E124" s="4" t="n">
+      <c r="E124" s="26" t="n">
         <v>220000000</v>
       </c>
-      <c r="F124" s="4" t="n">
+      <c r="F124" s="26" t="n">
         <v>16600000</v>
+      </c>
+      <c r="G124" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H124" s="23" t="inlineStr">
+        <is>
+          <t>2 FL offices (Tampa, Orlando) out of 69 total</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -4229,72 +5228,102 @@
       </c>
     </row>
     <row r="126">
-      <c r="B126" s="4" t="inlineStr">
+      <c r="B126" s="19" t="inlineStr">
         <is>
           <t>CFS</t>
         </is>
       </c>
-      <c r="C126" s="5" t="inlineStr">
+      <c r="C126" s="20" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D126" s="4" t="inlineStr">
+      <c r="D126" s="19" t="inlineStr">
         <is>
           <t>Boston, MA</t>
         </is>
       </c>
-      <c r="E126" s="4" t="n">
+      <c r="E126" s="19" t="n">
         <v>212000000</v>
       </c>
-      <c r="F126" s="4" t="n">
+      <c r="F126" s="19" t="n">
         <v>15000000</v>
       </c>
+      <c r="G126" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H126" s="18" t="inlineStr">
+        <is>
+          <t>3 FL offices: Orlando, Tampa, Fort Lauderdale</t>
+        </is>
+      </c>
     </row>
     <row r="127">
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B127" s="24" t="inlineStr">
         <is>
           <t>UniUni</t>
         </is>
       </c>
-      <c r="C127" s="3" t="inlineStr">
+      <c r="C127" s="25" t="inlineStr">
         <is>
           <t>Intermodal and Logistics Services</t>
         </is>
       </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="D127" s="24" t="inlineStr">
         <is>
           <t>Richmond, Canada</t>
         </is>
       </c>
-      <c r="E127" s="2" t="n">
+      <c r="E127" s="24" t="n">
         <v>208500000</v>
       </c>
-      <c r="F127" s="2" t="n">
+      <c r="F127" s="24" t="n">
         <v>14800000</v>
       </c>
+      <c r="G127" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H127" s="18" t="inlineStr">
+        <is>
+          <t>Miami was 1 of UniUni's initial US sorting centers; FL is 1 of 3 core expansion states (CA, TX, FL)</t>
+        </is>
+      </c>
     </row>
     <row r="128">
-      <c r="B128" s="4" t="inlineStr">
+      <c r="B128" s="26" t="inlineStr">
         <is>
           <t>Circle Logistics, Inc</t>
         </is>
       </c>
-      <c r="C128" s="5" t="inlineStr">
+      <c r="C128" s="27" t="inlineStr">
         <is>
           <t>Intermodal and Logistics Services</t>
         </is>
       </c>
-      <c r="D128" s="4" t="inlineStr">
+      <c r="D128" s="26" t="inlineStr">
         <is>
           <t>Fort Wayne, IN</t>
         </is>
       </c>
-      <c r="E128" s="4" t="n">
+      <c r="E128" s="26" t="n">
         <v>192700000</v>
       </c>
-      <c r="F128" s="4" t="n">
+      <c r="F128" s="26" t="n">
         <v>13600000</v>
+      </c>
+      <c r="G128" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H128" s="23" t="inlineStr">
+        <is>
+          <t>Orlando, FL office</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -4321,141 +5350,201 @@
       </c>
     </row>
     <row r="130">
-      <c r="B130" s="4" t="inlineStr">
+      <c r="B130" s="19" t="inlineStr">
         <is>
           <t>IDI: Insulation Distributors Inc.</t>
         </is>
       </c>
-      <c r="C130" s="5" t="inlineStr">
+      <c r="C130" s="20" t="inlineStr">
         <is>
           <t>Wholesale</t>
         </is>
       </c>
-      <c r="D130" s="4" t="inlineStr">
+      <c r="D130" s="19" t="inlineStr">
         <is>
           <t>Chanhassen, MN</t>
         </is>
       </c>
-      <c r="E130" s="4" t="n">
+      <c r="E130" s="19" t="n">
         <v>182100000</v>
       </c>
-      <c r="F130" s="4" t="n">
+      <c r="F130" s="19" t="n">
         <v>11400000</v>
       </c>
+      <c r="G130" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H130" s="18" t="inlineStr">
+        <is>
+          <t>4 FL branches: Jacksonville, Miami/Hollywood, Orlando, Tampa</t>
+        </is>
+      </c>
     </row>
     <row r="131">
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B131" s="24" t="inlineStr">
         <is>
           <t>Generator Supercenter</t>
         </is>
       </c>
-      <c r="C131" s="3" t="inlineStr">
+      <c r="C131" s="25" t="inlineStr">
         <is>
           <t>Specialty Retail</t>
         </is>
       </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="D131" s="24" t="inlineStr">
         <is>
           <t>Tomball, TX</t>
         </is>
       </c>
-      <c r="E131" s="2" t="n">
+      <c r="E131" s="24" t="n">
         <v>181900000</v>
       </c>
-      <c r="F131" s="2" t="n">
+      <c r="F131" s="24" t="n">
         <v>15400000</v>
       </c>
+      <c r="G131" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H131" s="18" t="inlineStr">
+        <is>
+          <t>5+ FL franchise stores: Miami, Hollywood, Ocala, Daytona/Port Orange, Orlando, Fort Myers area — hurricane-driven FL demand</t>
+        </is>
+      </c>
     </row>
     <row r="132">
-      <c r="B132" s="4" t="inlineStr">
+      <c r="B132" s="19" t="inlineStr">
         <is>
           <t>Skyline Exhibits</t>
         </is>
       </c>
-      <c r="C132" s="5" t="inlineStr">
+      <c r="C132" s="20" t="inlineStr">
         <is>
           <t>Event Management Services</t>
         </is>
       </c>
-      <c r="D132" s="4" t="inlineStr">
+      <c r="D132" s="19" t="inlineStr">
         <is>
           <t>Minnesota</t>
         </is>
       </c>
-      <c r="E132" s="4" t="n">
+      <c r="E132" s="19" t="n">
         <v>174800000</v>
       </c>
-      <c r="F132" s="4" t="n">
+      <c r="F132" s="19" t="n">
         <v>14200000</v>
       </c>
+      <c r="G132" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H132" s="18" t="inlineStr">
+        <is>
+          <t>Statewide dealer network: Skyline Exhibit Craft (Hallandale Beach — South FL + Caribbean) + Suncoast Displays (Tampa Bay, Sarasota, Orlando — 25+ years)</t>
+        </is>
+      </c>
     </row>
     <row r="133">
-      <c r="B133" s="4" t="inlineStr">
+      <c r="B133" s="19" t="inlineStr">
         <is>
           <t>Summit Fire &amp; Security</t>
         </is>
       </c>
-      <c r="C133" s="5" t="inlineStr">
+      <c r="C133" s="20" t="inlineStr">
         <is>
           <t>Defense &amp; Security</t>
         </is>
       </c>
-      <c r="D133" s="4" t="inlineStr">
+      <c r="D133" s="19" t="inlineStr">
         <is>
           <t>Reno, Nevada</t>
         </is>
       </c>
-      <c r="E133" s="4" t="n">
+      <c r="E133" s="19" t="n">
         <v>171100000</v>
       </c>
-      <c r="F133" s="4" t="n">
+      <c r="F133" s="19" t="n">
         <v>10800000</v>
       </c>
+      <c r="G133" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H133" s="18" t="inlineStr">
+        <is>
+          <t>7+ FL branches: Fort Lauderdale, Fort Myers, Orlando (2), Panama City Beach, Stuart, Tampa, Oakland Park; built via American Backflow + Mid State Fire acquisitions</t>
+        </is>
+      </c>
     </row>
     <row r="134">
-      <c r="B134" s="4" t="inlineStr">
+      <c r="B134" s="26" t="inlineStr">
         <is>
           <t>Rimkus</t>
         </is>
       </c>
-      <c r="C134" s="5" t="inlineStr">
+      <c r="C134" s="27" t="inlineStr">
         <is>
           <t>Legal Services</t>
         </is>
       </c>
-      <c r="D134" s="4" t="inlineStr">
+      <c r="D134" s="26" t="inlineStr">
         <is>
           <t>Houston, TX</t>
         </is>
       </c>
-      <c r="E134" s="4" t="n">
+      <c r="E134" s="26" t="n">
         <v>168200000</v>
       </c>
-      <c r="F134" s="4" t="n">
+      <c r="F134" s="26" t="n">
         <v>11200000</v>
       </c>
+      <c r="G134" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H134" s="23" t="inlineStr">
+        <is>
+          <t>2 FL offices: Doral/Miami and Tampa</t>
+        </is>
+      </c>
     </row>
     <row r="135">
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B135" s="24" t="inlineStr">
         <is>
           <t>IVX Health</t>
         </is>
       </c>
-      <c r="C135" s="3" t="inlineStr">
+      <c r="C135" s="25" t="inlineStr">
         <is>
           <t>Healthcare Facilities</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="D135" s="24" t="inlineStr">
         <is>
           <t>Brentwood, TN</t>
         </is>
       </c>
-      <c r="E135" s="2" t="n">
+      <c r="E135" s="24" t="n">
         <v>155800000</v>
       </c>
-      <c r="F135" s="2" t="n">
+      <c r="F135" s="24" t="n">
         <v>11400000</v>
+      </c>
+      <c r="G135" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H135" s="18" t="inlineStr">
+        <is>
+          <t>10+ FL infusion centers: Altamonte Springs, Orlando, Ft. Lauderdale (multiple), Daytona, Orange City, St. Augustine, Port St. Lucie, SW FL, North Central FL</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -4482,26 +5571,36 @@
       </c>
     </row>
     <row r="137">
-      <c r="B137" s="4" t="inlineStr">
+      <c r="B137" s="26" t="inlineStr">
         <is>
           <t>Gateway Services Inc.</t>
         </is>
       </c>
-      <c r="C137" s="5" t="inlineStr">
+      <c r="C137" s="27" t="inlineStr">
         <is>
           <t>Veterinary Care Services</t>
         </is>
       </c>
-      <c r="D137" s="4" t="inlineStr">
+      <c r="D137" s="26" t="inlineStr">
         <is>
           <t>Guelph, Canada</t>
         </is>
       </c>
-      <c r="E137" s="4" t="n">
+      <c r="E137" s="26" t="n">
         <v>152600000</v>
       </c>
-      <c r="F137" s="4" t="n">
+      <c r="F137" s="26" t="n">
         <v>14700000</v>
+      </c>
+      <c r="G137" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H137" s="23" t="inlineStr">
+        <is>
+          <t>Pet aftercare facilities in FL as part of 150+ location network</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -4528,94 +5627,124 @@
       </c>
     </row>
     <row r="139">
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B139" s="21" t="inlineStr">
         <is>
           <t>WATG and Wimberly Interiors</t>
         </is>
       </c>
-      <c r="C139" s="3" t="inlineStr">
+      <c r="C139" s="22" t="inlineStr">
         <is>
           <t>Architectural &amp; Engineering Services</t>
         </is>
       </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="D139" s="21" t="inlineStr">
         <is>
           <t>Tustin, CA</t>
         </is>
       </c>
-      <c r="E139" s="2" t="n">
+      <c r="E139" s="21" t="n">
         <v>147700000</v>
       </c>
-      <c r="F139" s="2" t="n">
+      <c r="F139" s="21" t="n">
         <v>13200000</v>
       </c>
+      <c r="G139" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H139" s="23" t="inlineStr">
+        <is>
+          <t>1 FL office in Coral Gables/Miami (210 Valencia Ave)</t>
+        </is>
+      </c>
     </row>
     <row r="140">
-      <c r="B140" s="4" t="inlineStr">
+      <c r="B140" s="26" t="inlineStr">
         <is>
           <t>Ole Mexican Foods Inc</t>
         </is>
       </c>
-      <c r="C140" s="5" t="inlineStr">
+      <c r="C140" s="27" t="inlineStr">
         <is>
           <t>Food &amp; Beverage Products</t>
         </is>
       </c>
-      <c r="D140" s="4" t="inlineStr">
+      <c r="D140" s="26" t="inlineStr">
         <is>
           <t>Grand Prairie, TX</t>
         </is>
       </c>
-      <c r="E140" s="4" t="n">
+      <c r="E140" s="26" t="n">
         <v>140200000</v>
       </c>
-      <c r="F140" s="4" t="n">
+      <c r="F140" s="26" t="n">
         <v>15500000</v>
       </c>
+      <c r="G140" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H140" s="23" t="inlineStr">
+        <is>
+          <t>Distribution center in Plant City, FL servicing Southeast retail</t>
+        </is>
+      </c>
     </row>
     <row r="141">
-      <c r="B141" s="4" t="inlineStr">
+      <c r="B141" s="19" t="inlineStr">
         <is>
           <t>Capital Vacations</t>
         </is>
       </c>
-      <c r="C141" s="5" t="inlineStr">
+      <c r="C141" s="20" t="inlineStr">
         <is>
           <t>Hotels &amp; Resorts</t>
         </is>
       </c>
-      <c r="D141" s="4" t="inlineStr">
+      <c r="D141" s="19" t="inlineStr">
         <is>
           <t>Myrtle Beach, SC</t>
         </is>
       </c>
-      <c r="E141" s="4" t="n">
+      <c r="E141" s="19" t="n">
         <v>136900000</v>
       </c>
-      <c r="F141" s="4" t="n">
+      <c r="F141" s="19" t="n">
         <v>12300000</v>
       </c>
+      <c r="G141" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H141" s="18" t="inlineStr">
+        <is>
+          <t>Manages 14+ resorts across FL: Cocoa Beach, Destin, Ft. Lauderdale, Palm Beach Shores, Panama City, Kissimmee/Calypso Cay</t>
+        </is>
+      </c>
     </row>
     <row r="142">
-      <c r="B142" s="14" t="inlineStr">
+      <c r="B142" s="19" t="inlineStr">
         <is>
           <t>Brightway Insurance</t>
         </is>
       </c>
-      <c r="C142" s="15" t="inlineStr">
+      <c r="C142" s="20" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D142" s="14" t="inlineStr">
+      <c r="D142" s="19" t="inlineStr">
         <is>
           <t>Jacksonville, FL</t>
         </is>
       </c>
-      <c r="E142" s="14" t="n">
+      <c r="E142" s="19" t="n">
         <v>134199999</v>
       </c>
-      <c r="F142" s="14" t="n">
+      <c r="F142" s="19" t="n">
         <v>8100000</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
@@ -4623,78 +5752,98 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H142" s="13" t="inlineStr">
+      <c r="H142" s="18" t="inlineStr">
         <is>
           <t>HQ in Jacksonville, FL</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B143" s="21" t="inlineStr">
         <is>
           <t>Adecco Permanent Recruitment</t>
         </is>
       </c>
-      <c r="C143" s="3" t="inlineStr">
+      <c r="C143" s="22" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="D143" s="21" t="inlineStr">
         <is>
           <t>Lisbon, Portugal</t>
         </is>
       </c>
-      <c r="E143" s="2" t="n">
+      <c r="E143" s="21" t="n">
         <v>117000000</v>
       </c>
-      <c r="F143" s="2" t="n">
+      <c r="F143" s="21" t="n">
         <v>8900000</v>
       </c>
+      <c r="G143" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H143" s="23" t="inlineStr">
+        <is>
+          <t>7+ FL branches: Orlando (2), Miami, Tampa, Plantation, Pinellas Park, Plant City, Davenport</t>
+        </is>
+      </c>
     </row>
     <row r="144">
-      <c r="B144" s="4" t="inlineStr">
+      <c r="B144" s="19" t="inlineStr">
         <is>
           <t>TEKsystems</t>
         </is>
       </c>
-      <c r="C144" s="5" t="inlineStr">
+      <c r="C144" s="20" t="inlineStr">
         <is>
           <t>IT Services</t>
         </is>
       </c>
-      <c r="D144" s="4" t="inlineStr">
+      <c r="D144" s="19" t="inlineStr">
         <is>
           <t>Hanover, MD</t>
         </is>
       </c>
-      <c r="E144" s="4" t="n">
+      <c r="E144" s="19" t="n">
         <v>113600000</v>
       </c>
-      <c r="F144" s="4" t="n">
+      <c r="F144" s="19" t="n">
         <v>8400000</v>
       </c>
+      <c r="G144" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H144" s="18" t="inlineStr">
+        <is>
+          <t>8+ FL offices: Jacksonville, Tampa, Miami, Maitland, Orlando, Pensacola, Tallahassee, Miramar</t>
+        </is>
+      </c>
     </row>
     <row r="145">
-      <c r="B145" s="14" t="inlineStr">
+      <c r="B145" s="19" t="inlineStr">
         <is>
           <t>Aline Accounting Partners</t>
         </is>
       </c>
-      <c r="C145" s="15" t="inlineStr">
+      <c r="C145" s="20" t="inlineStr">
         <is>
           <t>Accounting &amp; Financial Services</t>
         </is>
       </c>
-      <c r="D145" s="14" t="inlineStr">
+      <c r="D145" s="19" t="inlineStr">
         <is>
           <t>Tampa, FL</t>
         </is>
       </c>
-      <c r="E145" s="14" t="n">
+      <c r="E145" s="19" t="n">
         <v>108400000</v>
       </c>
-      <c r="F145" s="14" t="n">
+      <c r="F145" s="19" t="n">
         <v>5300000</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
@@ -4702,7 +5851,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H145" s="13" t="inlineStr">
+      <c r="H145" s="18" t="inlineStr">
         <is>
           <t>HQ in Tampa, FL</t>
         </is>
@@ -4732,25 +5881,25 @@
       </c>
     </row>
     <row r="147">
-      <c r="B147" s="14" t="inlineStr">
+      <c r="B147" s="19" t="inlineStr">
         <is>
           <t>Kforce Inc</t>
         </is>
       </c>
-      <c r="C147" s="15" t="inlineStr">
+      <c r="C147" s="20" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D147" s="14" t="inlineStr">
+      <c r="D147" s="19" t="inlineStr">
         <is>
           <t>Tampa, FL</t>
         </is>
       </c>
-      <c r="E147" s="14" t="n">
+      <c r="E147" s="19" t="n">
         <v>107700000</v>
       </c>
-      <c r="F147" s="14" t="n">
+      <c r="F147" s="19" t="n">
         <v>7000000</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
@@ -4758,78 +5907,98 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H147" s="13" t="inlineStr">
+      <c r="H147" s="18" t="inlineStr">
         <is>
           <t>HQ in Tampa, FL</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="B148" s="4" t="inlineStr">
+      <c r="B148" s="26" t="inlineStr">
         <is>
           <t>Global Medical Response</t>
         </is>
       </c>
-      <c r="C148" s="5" t="inlineStr">
+      <c r="C148" s="27" t="inlineStr">
         <is>
           <t>Healthcare &amp; Social Services</t>
         </is>
       </c>
-      <c r="D148" s="4" t="inlineStr">
+      <c r="D148" s="26" t="inlineStr">
         <is>
           <t>Lewisville, TX</t>
         </is>
       </c>
-      <c r="E148" s="4" t="n">
+      <c r="E148" s="26" t="n">
         <v>106700000</v>
       </c>
-      <c r="F148" s="4" t="n">
+      <c r="F148" s="26" t="n">
         <v>225700000</v>
       </c>
+      <c r="G148" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H148" s="23" t="inlineStr">
+        <is>
+          <t>AMR ground/air operations in FL across 46-state network</t>
+        </is>
+      </c>
     </row>
     <row r="149">
-      <c r="B149" s="4" t="inlineStr">
+      <c r="B149" s="19" t="inlineStr">
         <is>
           <t>AmTrust Financial Services, Inc.</t>
         </is>
       </c>
-      <c r="C149" s="5" t="inlineStr">
+      <c r="C149" s="20" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D149" s="4" t="inlineStr">
+      <c r="D149" s="19" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="E149" s="4" t="n">
+      <c r="E149" s="19" t="n">
         <v>105900000</v>
       </c>
-      <c r="F149" s="4" t="n">
+      <c r="F149" s="19" t="n">
         <v>6200000</v>
       </c>
+      <c r="G149" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H149" s="18" t="inlineStr">
+        <is>
+          <t>AmTrust North America of Florida, Inc. — registered FL subsidiary with 165+ employees at 901 W Yamato Rd, Boca Raton + offices in Orlando, Tampa</t>
+        </is>
+      </c>
     </row>
     <row r="150">
-      <c r="B150" s="10" t="inlineStr">
+      <c r="B150" s="24" t="inlineStr">
         <is>
           <t>Kavaliro</t>
         </is>
       </c>
-      <c r="C150" s="11" t="inlineStr">
+      <c r="C150" s="25" t="inlineStr">
         <is>
           <t>IT Services</t>
         </is>
       </c>
-      <c r="D150" s="10" t="inlineStr">
+      <c r="D150" s="24" t="inlineStr">
         <is>
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="E150" s="10" t="n">
+      <c r="E150" s="24" t="n">
         <v>99200000</v>
       </c>
-      <c r="F150" s="10" t="n">
+      <c r="F150" s="24" t="n">
         <v>7700000</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
@@ -4837,55 +6006,65 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H150" s="13" t="inlineStr">
+      <c r="H150" s="18" t="inlineStr">
         <is>
           <t>HQ in Orlando, FL</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="B151" s="4" t="inlineStr">
+      <c r="B151" s="19" t="inlineStr">
         <is>
           <t>Valcourt Group</t>
         </is>
       </c>
-      <c r="C151" s="5" t="inlineStr">
+      <c r="C151" s="20" t="inlineStr">
         <is>
           <t>Utility Services &amp; Equipment</t>
         </is>
       </c>
-      <c r="D151" s="4" t="inlineStr">
+      <c r="D151" s="19" t="inlineStr">
         <is>
           <t>McLean, VA</t>
         </is>
       </c>
-      <c r="E151" s="4" t="n">
+      <c r="E151" s="19" t="n">
         <v>97800000</v>
       </c>
-      <c r="F151" s="4" t="n">
+      <c r="F151" s="19" t="n">
         <v>7900000</v>
       </c>
+      <c r="G151" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H151" s="18" t="inlineStr">
+        <is>
+          <t>Major FL footprint — acquired A1 Orange; 3 FL offices (Jacksonville, Orlando, Tampa) explicitly described as a 'Florida footprint expansion'</t>
+        </is>
+      </c>
     </row>
     <row r="152">
-      <c r="B152" s="14" t="inlineStr">
+      <c r="B152" s="19" t="inlineStr">
         <is>
           <t>Elevated Facility Services</t>
         </is>
       </c>
-      <c r="C152" s="15" t="inlineStr">
+      <c r="C152" s="20" t="inlineStr">
         <is>
           <t>Utility Services &amp; Equipment</t>
         </is>
       </c>
-      <c r="D152" s="14" t="inlineStr">
+      <c r="D152" s="19" t="inlineStr">
         <is>
           <t>Tampa, FL</t>
         </is>
       </c>
-      <c r="E152" s="14" t="n">
+      <c r="E152" s="19" t="n">
         <v>96800000</v>
       </c>
-      <c r="F152" s="14" t="n">
+      <c r="F152" s="19" t="n">
         <v>9600000</v>
       </c>
       <c r="G152" s="12" t="inlineStr">
@@ -4893,101 +6072,131 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H152" s="13" t="inlineStr">
+      <c r="H152" s="18" t="inlineStr">
         <is>
           <t>HQ in Tampa, FL</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="B153" s="4" t="inlineStr">
+      <c r="B153" s="19" t="inlineStr">
         <is>
           <t>Kaufman Dolowich LLP</t>
         </is>
       </c>
-      <c r="C153" s="5" t="inlineStr">
+      <c r="C153" s="20" t="inlineStr">
         <is>
           <t>Legal Services</t>
         </is>
       </c>
-      <c r="D153" s="4" t="inlineStr">
+      <c r="D153" s="19" t="inlineStr">
         <is>
           <t>Woodbury, NY</t>
         </is>
       </c>
-      <c r="E153" s="4" t="n">
+      <c r="E153" s="19" t="n">
         <v>93500000</v>
       </c>
-      <c r="F153" s="4" t="n">
+      <c r="F153" s="19" t="n">
         <v>7500000</v>
       </c>
+      <c r="G153" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H153" s="18" t="inlineStr">
+        <is>
+          <t>2 FL offices (Orlando + Fort Lauderdale) with dedicated co-managing partners</t>
+        </is>
+      </c>
     </row>
     <row r="154">
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B154" s="24" t="inlineStr">
         <is>
           <t>Summit Fire Protection</t>
         </is>
       </c>
-      <c r="C154" s="3" t="inlineStr">
+      <c r="C154" s="25" t="inlineStr">
         <is>
           <t>Utility Services &amp; Equipment</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="D154" s="24" t="inlineStr">
         <is>
           <t>Saint Paul, MN</t>
         </is>
       </c>
-      <c r="E154" s="2" t="n">
+      <c r="E154" s="24" t="n">
         <v>89700000</v>
       </c>
-      <c r="F154" s="2" t="n">
+      <c r="F154" s="24" t="n">
         <v>7200000</v>
       </c>
+      <c r="G154" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H154" s="18" t="inlineStr">
+        <is>
+          <t>Entered FL via Republic Fire Protection + Fire Ranger acquisitions; 6+ FL branches: Jacksonville, Orlando (2), Tampa, Stuart, Fort Myers, Fort Lauderdale</t>
+        </is>
+      </c>
     </row>
     <row r="155">
-      <c r="B155" s="4" t="inlineStr">
+      <c r="B155" s="26" t="inlineStr">
         <is>
           <t>Fusion92</t>
         </is>
       </c>
-      <c r="C155" s="5" t="inlineStr">
+      <c r="C155" s="27" t="inlineStr">
         <is>
           <t>Advertising, Marketing, &amp; PR</t>
         </is>
       </c>
-      <c r="D155" s="4" t="inlineStr">
+      <c r="D155" s="26" t="inlineStr">
         <is>
           <t>Chicago, IL</t>
         </is>
       </c>
-      <c r="E155" s="4" t="n">
+      <c r="E155" s="26" t="n">
         <v>89000000</v>
       </c>
-      <c r="F155" s="4" t="n">
+      <c r="F155" s="26" t="n">
         <v>11500000</v>
       </c>
+      <c r="G155" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H155" s="23" t="inlineStr">
+        <is>
+          <t>Listed Bradenton, FL address</t>
+        </is>
+      </c>
     </row>
     <row r="156">
-      <c r="B156" s="14" t="inlineStr">
+      <c r="B156" s="19" t="inlineStr">
         <is>
           <t>Exploria Resorts</t>
         </is>
       </c>
-      <c r="C156" s="15" t="inlineStr">
+      <c r="C156" s="20" t="inlineStr">
         <is>
           <t>Hotels &amp; Resorts</t>
         </is>
       </c>
-      <c r="D156" s="14" t="inlineStr">
+      <c r="D156" s="19" t="inlineStr">
         <is>
           <t>Clermont, FL</t>
         </is>
       </c>
-      <c r="E156" s="14" t="n">
+      <c r="E156" s="19" t="n">
         <v>85300000</v>
       </c>
-      <c r="F156" s="14" t="n">
+      <c r="F156" s="19" t="n">
         <v>8500000</v>
       </c>
       <c r="G156" s="12" t="inlineStr">
@@ -4995,32 +6204,32 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H156" s="13" t="inlineStr">
+      <c r="H156" s="18" t="inlineStr">
         <is>
           <t>HQ in Clermont, FL</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="B157" s="10" t="inlineStr">
+      <c r="B157" s="24" t="inlineStr">
         <is>
           <t>4 Corner Resources</t>
         </is>
       </c>
-      <c r="C157" s="11" t="inlineStr">
+      <c r="C157" s="25" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D157" s="10" t="inlineStr">
+      <c r="D157" s="24" t="inlineStr">
         <is>
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="E157" s="10" t="n">
+      <c r="E157" s="24" t="n">
         <v>83800000</v>
       </c>
-      <c r="F157" s="10" t="n">
+      <c r="F157" s="24" t="n">
         <v>6800000</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
@@ -5028,33 +6237,43 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H157" s="13" t="inlineStr">
+      <c r="H157" s="18" t="inlineStr">
         <is>
           <t>HQ in Orlando, FL</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="B158" s="4" t="inlineStr">
+      <c r="B158" s="19" t="inlineStr">
         <is>
           <t>Lincoln Property Company</t>
         </is>
       </c>
-      <c r="C158" s="5" t="inlineStr">
+      <c r="C158" s="20" t="inlineStr">
         <is>
           <t>Real Estate Development</t>
         </is>
       </c>
-      <c r="D158" s="4" t="inlineStr">
+      <c r="D158" s="19" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
       </c>
-      <c r="E158" s="4" t="n">
+      <c r="E158" s="19" t="n">
         <v>82500000</v>
       </c>
-      <c r="F158" s="4" t="n">
+      <c r="F158" s="19" t="n">
         <v>4500000</v>
+      </c>
+      <c r="G158" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H158" s="18" t="inlineStr">
+        <is>
+          <t>FL designated as strategic growth market with dedicated Market Partner (Diego Juncadella); South FL portfolio 8M+ sqft (top-10 regional operator); offices in Miami, Tampa, St. Petersburg + Deerfield industrial acquisition</t>
+        </is>
       </c>
     </row>
     <row r="159">
@@ -5104,26 +6323,36 @@
       </c>
     </row>
     <row r="161">
-      <c r="B161" s="4" t="inlineStr">
+      <c r="B161" s="26" t="inlineStr">
         <is>
           <t>Randstad USA</t>
         </is>
       </c>
-      <c r="C161" s="5" t="inlineStr">
+      <c r="C161" s="27" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D161" s="4" t="inlineStr">
+      <c r="D161" s="26" t="inlineStr">
         <is>
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="E161" s="4" t="n">
+      <c r="E161" s="26" t="n">
         <v>76400000</v>
       </c>
-      <c r="F161" s="4" t="n">
+      <c r="F161" s="26" t="n">
         <v>5000000</v>
+      </c>
+      <c r="G161" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H161" s="23" t="inlineStr">
+        <is>
+          <t>Tampa + Jacksonville-area offices</t>
+        </is>
       </c>
     </row>
     <row r="162">
@@ -5150,49 +6379,69 @@
       </c>
     </row>
     <row r="163">
-      <c r="B163" s="4" t="inlineStr">
+      <c r="B163" s="26" t="inlineStr">
         <is>
           <t>Admiral Security Services</t>
         </is>
       </c>
-      <c r="C163" s="5" t="inlineStr">
+      <c r="C163" s="27" t="inlineStr">
         <is>
           <t>Private Security Services</t>
         </is>
       </c>
-      <c r="D163" s="4" t="inlineStr">
+      <c r="D163" s="26" t="inlineStr">
         <is>
           <t>Bethesda, MD</t>
         </is>
       </c>
-      <c r="E163" s="4" t="n">
+      <c r="E163" s="26" t="n">
         <v>72500000</v>
       </c>
-      <c r="F163" s="4" t="n">
+      <c r="F163" s="26" t="n">
         <v>5200000</v>
       </c>
+      <c r="G163" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H163" s="23" t="inlineStr">
+        <is>
+          <t>FL among state footprint (DE, DC, VA, WV, PA, NC, SC, NJ, NY, MA, FL, TX); Tampa presence confirmed</t>
+        </is>
+      </c>
     </row>
     <row r="164">
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B164" s="21" t="inlineStr">
         <is>
           <t>Syneos Health Commercial Solutions</t>
         </is>
       </c>
-      <c r="C164" s="3" t="inlineStr">
+      <c r="C164" s="22" t="inlineStr">
         <is>
           <t>Education &amp; Research</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="D164" s="21" t="inlineStr">
         <is>
           <t>Morrisville, NC</t>
         </is>
       </c>
-      <c r="E164" s="2" t="n">
+      <c r="E164" s="21" t="n">
         <v>67400000</v>
       </c>
-      <c r="F164" s="2" t="n">
+      <c r="F164" s="21" t="n">
         <v>1000000</v>
+      </c>
+      <c r="G164" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H164" s="23" t="inlineStr">
+        <is>
+          <t>Jacksonville office confirmed (1 of 69 global locations)</t>
+        </is>
       </c>
     </row>
     <row r="165">
@@ -5219,49 +6468,69 @@
       </c>
     </row>
     <row r="166">
-      <c r="B166" s="4" t="inlineStr">
+      <c r="B166" s="19" t="inlineStr">
         <is>
           <t>ISEC, Inc.</t>
         </is>
       </c>
-      <c r="C166" s="5" t="inlineStr">
+      <c r="C166" s="20" t="inlineStr">
         <is>
           <t>Construction &amp; Engineering</t>
         </is>
       </c>
-      <c r="D166" s="4" t="inlineStr">
+      <c r="D166" s="19" t="inlineStr">
         <is>
           <t>Greenwood Village, CO</t>
         </is>
       </c>
-      <c r="E166" s="4" t="n">
+      <c r="E166" s="19" t="n">
         <v>66599999</v>
       </c>
-      <c r="F166" s="4" t="n">
+      <c r="F166" s="19" t="n">
         <v>3900000</v>
       </c>
+      <c r="G166" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H166" s="18" t="inlineStr">
+        <is>
+          <t>3 FL offices: Tampa (Southeast regional HQ), Orlando, Fort Lauderdale</t>
+        </is>
+      </c>
     </row>
     <row r="167">
-      <c r="B167" s="4" t="inlineStr">
+      <c r="B167" s="19" t="inlineStr">
         <is>
           <t>ProDrivers</t>
         </is>
       </c>
-      <c r="C167" s="5" t="inlineStr">
+      <c r="C167" s="20" t="inlineStr">
         <is>
           <t>Road Transportation</t>
         </is>
       </c>
-      <c r="D167" s="4" t="inlineStr">
+      <c r="D167" s="19" t="inlineStr">
         <is>
           <t>Atlanta, GA</t>
         </is>
       </c>
-      <c r="E167" s="4" t="n">
+      <c r="E167" s="19" t="n">
         <v>64200000</v>
       </c>
-      <c r="F167" s="4" t="n">
+      <c r="F167" s="19" t="n">
         <v>4800000</v>
+      </c>
+      <c r="G167" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H167" s="18" t="inlineStr">
+        <is>
+          <t>Multiple FL branches: Orlando, Miami/Hialeah, Jacksonville, Fort Lauderdale, Stuart</t>
+        </is>
       </c>
     </row>
     <row r="168">
@@ -5311,48 +6580,58 @@
       </c>
     </row>
     <row r="170">
-      <c r="B170" s="4" t="inlineStr">
+      <c r="B170" s="19" t="inlineStr">
         <is>
           <t>Raphael &amp; Associates</t>
         </is>
       </c>
-      <c r="C170" s="5" t="inlineStr">
+      <c r="C170" s="20" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D170" s="4" t="inlineStr">
+      <c r="D170" s="19" t="inlineStr">
         <is>
           <t>Rutherford, NJ</t>
         </is>
       </c>
-      <c r="E170" s="4" t="n">
+      <c r="E170" s="19" t="n">
         <v>60800000</v>
       </c>
-      <c r="F170" s="4" t="n">
+      <c r="F170" s="19" t="n">
         <v>5600000</v>
       </c>
+      <c r="G170" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H170" s="18" t="inlineStr">
+        <is>
+          <t>2 dedicated FL claims offices: Lake Mary/Orlando + Pinecrest/Miami</t>
+        </is>
+      </c>
     </row>
     <row r="171">
-      <c r="B171" s="14" t="inlineStr">
+      <c r="B171" s="19" t="inlineStr">
         <is>
           <t>ASB FINANCIAL</t>
         </is>
       </c>
-      <c r="C171" s="15" t="inlineStr">
+      <c r="C171" s="20" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D171" s="14" t="inlineStr">
+      <c r="D171" s="19" t="inlineStr">
         <is>
           <t>Ocala, FL</t>
         </is>
       </c>
-      <c r="E171" s="14" t="n">
+      <c r="E171" s="19" t="n">
         <v>57600000</v>
       </c>
-      <c r="F171" s="14" t="n">
+      <c r="F171" s="19" t="n">
         <v>5300000</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
@@ -5360,79 +6639,109 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H171" s="13" t="inlineStr">
+      <c r="H171" s="18" t="inlineStr">
         <is>
           <t>HQ in Ocala, FL</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="B172" s="2" t="inlineStr">
+      <c r="B172" s="21" t="inlineStr">
         <is>
           <t>Premier Trailer Leasing</t>
         </is>
       </c>
-      <c r="C172" s="3" t="inlineStr">
+      <c r="C172" s="22" t="inlineStr">
         <is>
           <t>Road Transportation</t>
         </is>
       </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="D172" s="21" t="inlineStr">
         <is>
           <t>Plano, TX</t>
         </is>
       </c>
-      <c r="E172" s="2" t="n">
+      <c r="E172" s="21" t="n">
         <v>50400000</v>
       </c>
-      <c r="F172" s="2" t="n">
+      <c r="F172" s="21" t="n">
         <v>3100000</v>
       </c>
+      <c r="G172" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H172" s="23" t="inlineStr">
+        <is>
+          <t>2 FL branches: Orlando + Tampa</t>
+        </is>
+      </c>
     </row>
     <row r="173">
-      <c r="B173" s="4" t="inlineStr">
+      <c r="B173" s="19" t="inlineStr">
         <is>
           <t>Odevo</t>
         </is>
       </c>
-      <c r="C173" s="5" t="inlineStr">
+      <c r="C173" s="20" t="inlineStr">
         <is>
           <t>Real Estate Development</t>
         </is>
       </c>
-      <c r="D173" s="4" t="inlineStr">
+      <c r="D173" s="19" t="inlineStr">
         <is>
           <t>Stockholm, Sweden</t>
         </is>
       </c>
-      <c r="E173" s="4" t="n">
+      <c r="E173" s="19" t="n">
         <v>45300000</v>
       </c>
-      <c r="F173" s="4" t="n">
+      <c r="F173" s="19" t="n">
         <v>2800000</v>
       </c>
+      <c r="G173" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H173" s="18" t="inlineStr">
+        <is>
+          <t>Entered US by acquiring Miami-based KW Property Management &amp; Consulting (KWPMC); 130,000+ FL homes under management</t>
+        </is>
+      </c>
     </row>
     <row r="174">
-      <c r="B174" s="4" t="inlineStr">
+      <c r="B174" s="19" t="inlineStr">
         <is>
           <t>Landscape Workshop</t>
         </is>
       </c>
-      <c r="C174" s="5" t="inlineStr">
+      <c r="C174" s="20" t="inlineStr">
         <is>
           <t>Waste Management Services</t>
         </is>
       </c>
-      <c r="D174" s="4" t="inlineStr">
+      <c r="D174" s="19" t="inlineStr">
         <is>
           <t>Birmingham, AL</t>
         </is>
       </c>
-      <c r="E174" s="4" t="n">
+      <c r="E174" s="19" t="n">
         <v>45200000</v>
       </c>
-      <c r="F174" s="4" t="n">
+      <c r="F174" s="19" t="n">
         <v>3400000</v>
+      </c>
+      <c r="G174" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H174" s="18" t="inlineStr">
+        <is>
+          <t>Florida is an explicit service region — 'South Florida and the Florida panhandle' with dedicated FL branch page</t>
+        </is>
       </c>
     </row>
     <row r="175">
@@ -5459,72 +6768,102 @@
       </c>
     </row>
     <row r="176">
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B176" s="24" t="inlineStr">
         <is>
           <t>Mass Markets</t>
         </is>
       </c>
-      <c r="C176" s="3" t="inlineStr">
+      <c r="C176" s="25" t="inlineStr">
         <is>
           <t>IT Services</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="D176" s="24" t="inlineStr">
         <is>
           <t>Iowa City, Iowa</t>
         </is>
       </c>
-      <c r="E176" s="2" t="n">
+      <c r="E176" s="24" t="n">
         <v>43500000</v>
       </c>
-      <c r="F176" s="2" t="n">
+      <c r="F176" s="24" t="n">
         <v>3400000</v>
       </c>
+      <c r="G176" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H176" s="18" t="inlineStr">
+        <is>
+          <t>FL explicitly named as 1 of 4 core service delivery states ('thousands of seats throughout CO, IA, FL, SD')</t>
+        </is>
+      </c>
     </row>
     <row r="177">
-      <c r="B177" s="4" t="inlineStr">
+      <c r="B177" s="26" t="inlineStr">
         <is>
           <t>Merino Consulting Services</t>
         </is>
       </c>
-      <c r="C177" s="5" t="inlineStr">
+      <c r="C177" s="27" t="inlineStr">
         <is>
           <t>IT Services</t>
         </is>
       </c>
-      <c r="D177" s="4" t="inlineStr">
+      <c r="D177" s="26" t="inlineStr">
         <is>
           <t>New Delhi, India</t>
         </is>
       </c>
-      <c r="E177" s="4" t="n">
+      <c r="E177" s="26" t="n">
         <v>42700000</v>
       </c>
-      <c r="F177" s="4" t="n">
+      <c r="F177" s="26" t="n">
         <v>3300000</v>
       </c>
+      <c r="G177" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H177" s="23" t="inlineStr">
+        <is>
+          <t>Orlando office (4700 Millenia Blvd) — primary US office</t>
+        </is>
+      </c>
     </row>
     <row r="178">
-      <c r="B178" s="4" t="inlineStr">
+      <c r="B178" s="19" t="inlineStr">
         <is>
           <t>Easy Ice</t>
         </is>
       </c>
-      <c r="C178" s="5" t="inlineStr">
+      <c r="C178" s="20" t="inlineStr">
         <is>
           <t>Food &amp; Beverage Products</t>
         </is>
       </c>
-      <c r="D178" s="4" t="inlineStr">
+      <c r="D178" s="19" t="inlineStr">
         <is>
           <t>Marquette, MI</t>
         </is>
       </c>
-      <c r="E178" s="4" t="n">
+      <c r="E178" s="19" t="n">
         <v>40500000</v>
       </c>
-      <c r="F178" s="4" t="n">
+      <c r="F178" s="19" t="n">
         <v>3900000</v>
+      </c>
+      <c r="G178" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H178" s="18" t="inlineStr">
+        <is>
+          <t>1 of ~6 dedicated US warehouse/distribution facilities in Orlando, FL</t>
+        </is>
       </c>
     </row>
     <row r="179">
@@ -5574,163 +6913,223 @@
       </c>
     </row>
     <row r="181">
-      <c r="B181" s="4" t="inlineStr">
+      <c r="B181" s="26" t="inlineStr">
         <is>
           <t>swipejobs</t>
         </is>
       </c>
-      <c r="C181" s="5" t="inlineStr">
+      <c r="C181" s="27" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D181" s="4" t="inlineStr">
+      <c r="D181" s="26" t="inlineStr">
         <is>
           <t>North Sydney, Australia</t>
         </is>
       </c>
-      <c r="E181" s="4" t="n">
+      <c r="E181" s="26" t="n">
         <v>32900000</v>
       </c>
-      <c r="F181" s="4" t="n">
+      <c r="F181" s="26" t="n">
         <v>2500000</v>
       </c>
+      <c r="G181" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H181" s="23" t="inlineStr">
+        <is>
+          <t>Registered FL entity in Plantation + Orlando/Apopka job operations</t>
+        </is>
+      </c>
     </row>
     <row r="182">
-      <c r="B182" s="4" t="inlineStr">
+      <c r="B182" s="19" t="inlineStr">
         <is>
           <t>Surface Experts</t>
         </is>
       </c>
-      <c r="C182" s="5" t="inlineStr">
+      <c r="C182" s="20" t="inlineStr">
         <is>
           <t>Consumer Durable Services</t>
         </is>
       </c>
-      <c r="D182" s="4" t="inlineStr">
+      <c r="D182" s="19" t="inlineStr">
         <is>
           <t>Spokane, WA</t>
         </is>
       </c>
-      <c r="E182" s="4" t="n">
+      <c r="E182" s="19" t="n">
         <v>32299999</v>
       </c>
-      <c r="F182" s="4" t="n">
+      <c r="F182" s="19" t="n">
         <v>3200000</v>
       </c>
+      <c r="G182" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H182" s="18" t="inlineStr">
+        <is>
+          <t>Multiple FL franchise territories: East Orlando (2020), Coastal SE FL/Miami-Ft. Lauderdale (2021), Seminole/Volusia (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="183">
-      <c r="B183" s="4" t="inlineStr">
+      <c r="B183" s="26" t="inlineStr">
         <is>
           <t>USA Insulation</t>
         </is>
       </c>
-      <c r="C183" s="5" t="inlineStr">
+      <c r="C183" s="27" t="inlineStr">
         <is>
           <t>Consumer Durable Services</t>
         </is>
       </c>
-      <c r="D183" s="4" t="inlineStr">
+      <c r="D183" s="26" t="inlineStr">
         <is>
           <t>Cleveland, OH</t>
         </is>
       </c>
-      <c r="E183" s="4" t="n">
+      <c r="E183" s="26" t="n">
         <v>32000000</v>
       </c>
-      <c r="F183" s="4" t="n">
+      <c r="F183" s="26" t="n">
         <v>3200000</v>
       </c>
+      <c r="G183" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H183" s="23" t="inlineStr">
+        <is>
+          <t>4 franchise territories in Tampa Bay (Hillsborough, Pinellas, Pasco) — first FL market entry</t>
+        </is>
+      </c>
     </row>
     <row r="184">
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B184" s="24" t="inlineStr">
         <is>
           <t>Weiser Security Services, Inc.</t>
         </is>
       </c>
-      <c r="C184" s="3" t="inlineStr">
+      <c r="C184" s="25" t="inlineStr">
         <is>
           <t>Private Security Services</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D184" s="24" t="inlineStr">
         <is>
           <t>New Orleans, LA</t>
         </is>
       </c>
-      <c r="E184" s="2" t="n">
+      <c r="E184" s="24" t="n">
         <v>31000000</v>
       </c>
-      <c r="F184" s="2" t="n">
+      <c r="F184" s="24" t="n">
         <v>2200000</v>
       </c>
+      <c r="G184" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H184" s="18" t="inlineStr">
+        <is>
+          <t>6+ FL branches: Miami, Orlando, Fort Myers, Jacksonville, West Palm Beach, Tampa + operations in 10+ additional FL cities</t>
+        </is>
+      </c>
     </row>
     <row r="185">
-      <c r="B185" s="4" t="inlineStr">
+      <c r="B185" s="19" t="inlineStr">
         <is>
           <t>THS National</t>
         </is>
       </c>
-      <c r="C185" s="5" t="inlineStr">
+      <c r="C185" s="20" t="inlineStr">
         <is>
           <t>Construction &amp; Engineering</t>
         </is>
       </c>
-      <c r="D185" s="4" t="inlineStr">
+      <c r="D185" s="19" t="inlineStr">
         <is>
           <t>Apex, NC</t>
         </is>
       </c>
-      <c r="E185" s="4" t="n">
+      <c r="E185" s="19" t="n">
         <v>30300000</v>
       </c>
-      <c r="F185" s="4" t="n">
+      <c r="F185" s="19" t="n">
         <v>2100000</v>
       </c>
+      <c r="G185" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H185" s="18" t="inlineStr">
+        <is>
+          <t>Dedicated teams in Orlando, Tampa, South FL — FL is a core market for this multifamily GC</t>
+        </is>
+      </c>
     </row>
     <row r="186">
-      <c r="B186" s="4" t="inlineStr">
+      <c r="B186" s="26" t="inlineStr">
         <is>
           <t>Precise Systems, Inc.</t>
         </is>
       </c>
-      <c r="C186" s="5" t="inlineStr">
+      <c r="C186" s="27" t="inlineStr">
         <is>
           <t>Aerospace &amp; Defense</t>
         </is>
       </c>
-      <c r="D186" s="4" t="inlineStr">
+      <c r="D186" s="26" t="inlineStr">
         <is>
           <t>Lexington Park, MD</t>
         </is>
       </c>
-      <c r="E186" s="4" t="n">
+      <c r="E186" s="26" t="n">
         <v>29700000</v>
       </c>
-      <c r="F186" s="4" t="n">
+      <c r="F186" s="26" t="n">
         <v>1900000</v>
       </c>
+      <c r="G186" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H186" s="23" t="inlineStr">
+        <is>
+          <t>Orlando, FL office for IT services in addition to MD HQ</t>
+        </is>
+      </c>
     </row>
     <row r="187">
-      <c r="B187" s="10" t="inlineStr">
+      <c r="B187" s="24" t="inlineStr">
         <is>
           <t>Terra</t>
         </is>
       </c>
-      <c r="C187" s="11" t="inlineStr">
+      <c r="C187" s="25" t="inlineStr">
         <is>
           <t>Chips &amp; Semiconductors</t>
         </is>
       </c>
-      <c r="D187" s="10" t="inlineStr">
+      <c r="D187" s="24" t="inlineStr">
         <is>
           <t>Miami, FL</t>
         </is>
       </c>
-      <c r="E187" s="10" t="n">
+      <c r="E187" s="24" t="n">
         <v>29500000</v>
       </c>
-      <c r="F187" s="10" t="n">
+      <c r="F187" s="24" t="n">
         <v>2300000</v>
       </c>
       <c r="G187" s="12" t="inlineStr">
@@ -5738,32 +7137,32 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H187" s="13" t="inlineStr">
+      <c r="H187" s="18" t="inlineStr">
         <is>
           <t>HQ in Miami, FL</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="B188" s="14" t="inlineStr">
+      <c r="B188" s="19" t="inlineStr">
         <is>
           <t>Southern Roofing and Renovations</t>
         </is>
       </c>
-      <c r="C188" s="15" t="inlineStr">
+      <c r="C188" s="20" t="inlineStr">
         <is>
           <t>Construction &amp; Engineering</t>
         </is>
       </c>
-      <c r="D188" s="14" t="inlineStr">
+      <c r="D188" s="19" t="inlineStr">
         <is>
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="E188" s="14" t="n">
+      <c r="E188" s="19" t="n">
         <v>29500000</v>
       </c>
-      <c r="F188" s="14" t="n">
+      <c r="F188" s="19" t="n">
         <v>2500000</v>
       </c>
       <c r="G188" s="12" t="inlineStr">
@@ -5771,7 +7170,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H188" s="13" t="inlineStr">
+      <c r="H188" s="18" t="inlineStr">
         <is>
           <t>HQ in Orlando, FL</t>
         </is>
@@ -5801,48 +7200,58 @@
       </c>
     </row>
     <row r="190">
-      <c r="B190" s="4" t="inlineStr">
+      <c r="B190" s="19" t="inlineStr">
         <is>
           <t>Food Sales East</t>
         </is>
       </c>
-      <c r="C190" s="5" t="inlineStr">
+      <c r="C190" s="20" t="inlineStr">
         <is>
           <t>Food &amp; Beverage Products</t>
         </is>
       </c>
-      <c r="D190" s="4" t="inlineStr">
+      <c r="D190" s="19" t="inlineStr">
         <is>
           <t>Alabaster, AL</t>
         </is>
       </c>
-      <c r="E190" s="4" t="n">
+      <c r="E190" s="19" t="n">
         <v>27600000</v>
       </c>
-      <c r="F190" s="4" t="n">
+      <c r="F190" s="19" t="n">
         <v>2700000</v>
       </c>
+      <c r="G190" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H190" s="18" t="inlineStr">
+        <is>
+          <t>Dedicated FL offices: Orlando, Boynton Beach, Largo (FL is 1 of 9 core states)</t>
+        </is>
+      </c>
     </row>
     <row r="191">
-      <c r="B191" s="10" t="inlineStr">
+      <c r="B191" s="24" t="inlineStr">
         <is>
           <t>Medcom Benefit Solutions</t>
         </is>
       </c>
-      <c r="C191" s="11" t="inlineStr">
+      <c r="C191" s="25" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D191" s="10" t="inlineStr">
+      <c r="D191" s="24" t="inlineStr">
         <is>
           <t>Jacksonville, FL</t>
         </is>
       </c>
-      <c r="E191" s="10" t="n">
+      <c r="E191" s="24" t="n">
         <v>27400000</v>
       </c>
-      <c r="F191" s="10" t="n">
+      <c r="F191" s="24" t="n">
         <v>2300000</v>
       </c>
       <c r="G191" s="12" t="inlineStr">
@@ -5850,7 +7259,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H191" s="13" t="inlineStr">
+      <c r="H191" s="18" t="inlineStr">
         <is>
           <t>HQ in Jacksonville, FL</t>
         </is>
@@ -5880,72 +7289,102 @@
       </c>
     </row>
     <row r="193">
-      <c r="B193" s="4" t="inlineStr">
+      <c r="B193" s="19" t="inlineStr">
         <is>
           <t>Prism Specialties</t>
         </is>
       </c>
-      <c r="C193" s="5" t="inlineStr">
+      <c r="C193" s="20" t="inlineStr">
         <is>
           <t>Utility Services &amp; Equipment</t>
         </is>
       </c>
-      <c r="D193" s="4" t="inlineStr">
+      <c r="D193" s="19" t="inlineStr">
         <is>
           <t>Livonia, MI</t>
         </is>
       </c>
-      <c r="E193" s="4" t="n">
+      <c r="E193" s="19" t="n">
         <v>26600000</v>
       </c>
-      <c r="F193" s="4" t="n">
+      <c r="F193" s="19" t="n">
         <v>2600000</v>
       </c>
+      <c r="G193" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H193" s="18" t="inlineStr">
+        <is>
+          <t>4 FL franchise territories: Central FL (Tampa), Greater Orlando/Space/Treasure Coasts, Suncoast FL (Bradenton-Tampa), South FL</t>
+        </is>
+      </c>
     </row>
     <row r="194">
-      <c r="B194" s="4" t="inlineStr">
+      <c r="B194" s="26" t="inlineStr">
         <is>
           <t>CyberCoders</t>
         </is>
       </c>
-      <c r="C194" s="5" t="inlineStr">
+      <c r="C194" s="27" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D194" s="4" t="inlineStr">
+      <c r="D194" s="26" t="inlineStr">
         <is>
           <t>Irvine, CA</t>
         </is>
       </c>
-      <c r="E194" s="4" t="n">
+      <c r="E194" s="26" t="n">
         <v>25600000</v>
       </c>
-      <c r="F194" s="4" t="n">
+      <c r="F194" s="26" t="n">
         <v>1900000</v>
       </c>
+      <c r="G194" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H194" s="23" t="inlineStr">
+        <is>
+          <t>FL office reportedly opened in addition to CA/NY/Boston/LA</t>
+        </is>
+      </c>
     </row>
     <row r="195">
-      <c r="B195" s="2" t="inlineStr">
+      <c r="B195" s="21" t="inlineStr">
         <is>
           <t>PURIS</t>
         </is>
       </c>
-      <c r="C195" s="3" t="inlineStr">
+      <c r="C195" s="22" t="inlineStr">
         <is>
           <t>Utility Services &amp; Equipment</t>
         </is>
       </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="D195" s="21" t="inlineStr">
         <is>
           <t>The Woodlands, TX</t>
         </is>
       </c>
-      <c r="E195" s="2" t="n">
+      <c r="E195" s="21" t="n">
         <v>25500000</v>
       </c>
-      <c r="F195" s="2" t="n">
+      <c r="F195" s="21" t="n">
         <v>2100000</v>
+      </c>
+      <c r="G195" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H195" s="23" t="inlineStr">
+        <is>
+          <t>Sunrise, FL office; predecessor Murphy Pipeline Contractors was Jacksonville, FL-based (acquired 2020)</t>
+        </is>
       </c>
     </row>
     <row r="196">
@@ -5972,25 +7411,25 @@
       </c>
     </row>
     <row r="197">
-      <c r="B197" s="10" t="inlineStr">
+      <c r="B197" s="24" t="inlineStr">
         <is>
           <t>Allstates WorldCargo</t>
         </is>
       </c>
-      <c r="C197" s="11" t="inlineStr">
+      <c r="C197" s="25" t="inlineStr">
         <is>
           <t>Intermodal and Logistics Services</t>
         </is>
       </c>
-      <c r="D197" s="10" t="inlineStr">
+      <c r="D197" s="24" t="inlineStr">
         <is>
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="E197" s="10" t="n">
+      <c r="E197" s="24" t="n">
         <v>24000000</v>
       </c>
-      <c r="F197" s="10" t="n">
+      <c r="F197" s="24" t="n">
         <v>2500000</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
@@ -5998,78 +7437,98 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H197" s="13" t="inlineStr">
+      <c r="H197" s="18" t="inlineStr">
         <is>
           <t>HQ in Orlando, FL</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="B198" s="4" t="inlineStr">
+      <c r="B198" s="26" t="inlineStr">
         <is>
           <t>The Alliance Group</t>
         </is>
       </c>
-      <c r="C198" s="5" t="inlineStr">
+      <c r="C198" s="27" t="inlineStr">
         <is>
           <t>Management &amp; Strategy Consulting</t>
         </is>
       </c>
-      <c r="D198" s="4" t="inlineStr">
+      <c r="D198" s="26" t="inlineStr">
         <is>
           <t>Vienna, VA</t>
         </is>
       </c>
-      <c r="E198" s="4" t="n">
+      <c r="E198" s="26" t="n">
         <v>23500000</v>
       </c>
-      <c r="F198" s="4" t="n">
+      <c r="F198" s="26" t="n">
         <v>2900000</v>
       </c>
+      <c r="G198" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H198" s="23" t="inlineStr">
+        <is>
+          <t>Dedicated South Florida accounting/finance practice (150+ placements, $3M+ GP)</t>
+        </is>
+      </c>
     </row>
     <row r="199">
-      <c r="B199" s="4" t="inlineStr">
+      <c r="B199" s="26" t="inlineStr">
         <is>
           <t>Roo</t>
         </is>
       </c>
-      <c r="C199" s="5" t="inlineStr">
+      <c r="C199" s="27" t="inlineStr">
         <is>
           <t>Healthcare Facilities</t>
         </is>
       </c>
-      <c r="D199" s="4" t="inlineStr">
+      <c r="D199" s="26" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="E199" s="4" t="n">
+      <c r="E199" s="26" t="n">
         <v>23100000</v>
       </c>
-      <c r="F199" s="4" t="n">
+      <c r="F199" s="26" t="n">
         <v>2400000</v>
       </c>
+      <c r="G199" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="H199" s="23" t="inlineStr">
+        <is>
+          <t>Active in Tampa, Orlando, Lakeland FL veterinary markets with dedicated landing pages (platform business, no office)</t>
+        </is>
+      </c>
     </row>
     <row r="200">
-      <c r="B200" s="14" t="inlineStr">
+      <c r="B200" s="19" t="inlineStr">
         <is>
           <t>United Land Services</t>
         </is>
       </c>
-      <c r="C200" s="15" t="inlineStr">
+      <c r="C200" s="20" t="inlineStr">
         <is>
           <t>Utility Services &amp; Equipment</t>
         </is>
       </c>
-      <c r="D200" s="14" t="inlineStr">
+      <c r="D200" s="19" t="inlineStr">
         <is>
           <t>Jacksonville, FL</t>
         </is>
       </c>
-      <c r="E200" s="14" t="n">
+      <c r="E200" s="19" t="n">
         <v>22900000</v>
       </c>
-      <c r="F200" s="14" t="n">
+      <c r="F200" s="19" t="n">
         <v>2400000</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
@@ -6077,32 +7536,32 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H200" s="13" t="inlineStr">
+      <c r="H200" s="18" t="inlineStr">
         <is>
           <t>HQ in Jacksonville, FL</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="B201" s="10" t="inlineStr">
+      <c r="B201" s="24" t="inlineStr">
         <is>
           <t>KW PROPERTY MANAGEMENT AND CONSULTING</t>
         </is>
       </c>
-      <c r="C201" s="11" t="inlineStr">
+      <c r="C201" s="25" t="inlineStr">
         <is>
           <t>Management &amp; Strategy Consulting</t>
         </is>
       </c>
-      <c r="D201" s="10" t="inlineStr">
+      <c r="D201" s="24" t="inlineStr">
         <is>
           <t>Doral, FL</t>
         </is>
       </c>
-      <c r="E201" s="10" t="n">
+      <c r="E201" s="24" t="n">
         <v>22200000</v>
       </c>
-      <c r="F201" s="10" t="n">
+      <c r="F201" s="24" t="n">
         <v>2100000</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
@@ -6110,7 +7569,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H201" s="13" t="inlineStr">
+      <c r="H201" s="18" t="inlineStr">
         <is>
           <t>HQ in Doral, FL</t>
         </is>
@@ -6163,26 +7622,36 @@
       </c>
     </row>
     <row r="204">
-      <c r="B204" s="4" t="inlineStr">
+      <c r="B204" s="19" t="inlineStr">
         <is>
           <t>Synergy Interactive</t>
         </is>
       </c>
-      <c r="C204" s="5" t="inlineStr">
+      <c r="C204" s="20" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D204" s="4" t="inlineStr">
+      <c r="D204" s="19" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="E204" s="4" t="n">
+      <c r="E204" s="19" t="n">
         <v>17500000</v>
       </c>
-      <c r="F204" s="4" t="n">
+      <c r="F204" s="19" t="n">
         <v>1800000</v>
+      </c>
+      <c r="G204" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H204" s="18" t="inlineStr">
+        <is>
+          <t>Orlando, FL (121 S Orange Ave, Suite 850) — 1 of only 3 offices (NYC, FL, Nashville)</t>
+        </is>
       </c>
     </row>
     <row r="205">
@@ -6209,25 +7678,25 @@
       </c>
     </row>
     <row r="206">
-      <c r="B206" s="10" t="inlineStr">
+      <c r="B206" s="24" t="inlineStr">
         <is>
           <t>Crawford Thomas Recruiting</t>
         </is>
       </c>
-      <c r="C206" s="11" t="inlineStr">
+      <c r="C206" s="25" t="inlineStr">
         <is>
           <t>Human Resources &amp; Recruitment Services</t>
         </is>
       </c>
-      <c r="D206" s="10" t="inlineStr">
+      <c r="D206" s="24" t="inlineStr">
         <is>
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="E206" s="10" t="n">
+      <c r="E206" s="24" t="n">
         <v>16900000</v>
       </c>
-      <c r="F206" s="10" t="n">
+      <c r="F206" s="24" t="n">
         <v>1800000</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
@@ -6235,33 +7704,43 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H206" s="13" t="inlineStr">
+      <c r="H206" s="18" t="inlineStr">
         <is>
           <t>HQ in Orlando, FL</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="B207" s="6" t="inlineStr">
+      <c r="B207" s="28" t="inlineStr">
         <is>
           <t>St. Moritz Security Services, Inc.</t>
         </is>
       </c>
-      <c r="C207" s="7" t="inlineStr">
+      <c r="C207" s="29" t="inlineStr">
         <is>
           <t>Private Security Services</t>
         </is>
       </c>
-      <c r="D207" s="6" t="inlineStr">
+      <c r="D207" s="28" t="inlineStr">
         <is>
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="E207" s="6" t="n">
+      <c r="E207" s="28" t="n">
         <v>11000000</v>
       </c>
-      <c r="F207" s="6" t="n">
+      <c r="F207" s="28" t="n">
         <v>1100000</v>
+      </c>
+      <c r="G207" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H207" s="18" t="inlineStr">
+        <is>
+          <t>6 dedicated FL offices: Ft. Lauderdale/Miami, Naples/Ft. Myers, Orlando, Pensacola, Tampa, West Palm Beach + Lakeland</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Magic_B2B_Prospecting_FL_Highlighted.xlsx
+++ b/Magic_B2B_Prospecting_FL_Highlighted.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="0" xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="23385" tabRatio="0" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FL Highlights Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Prospecting List" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Prospecting List" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FL Highlights Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1264,140 +1264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>Florida-Connected B2B Prospects</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Legend</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>HQ in FL, dedicated FL business unit/subsidiary, multiple FL offices/branches as a top market, or FL explicitly cited as a strategic market</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>EDGE</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Some FL operational presence (1-2 offices, regional rep coverage, distribution touch-point) but FL is one of many markets — not dominant</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Counts</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>YES — 111 (28 HQ'd in FL + 83 with major FL operations)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>EDGE — 47</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NO — remaining rows (no meaningful FL connection)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>Methodology notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>Pass 1: auto-tagged all 29 companies with HQ listed in Florida (incl. Waste Pro USA — manual correction).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>Pass 2: dispatched 6 parallel research agents to assess the remaining ~177 non-FL-HQ companies for major FL operations (multiple FL offices/branches, FL-based subsidiary, FL acquisition history, FL named as top market).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>YES = strong evidence FL is a top-tier operational market. EDGE = some FL presence (1-2 offices, regional coverage) but not dominant. NO = no meaningful FL connection beyond standard nationwide footprint.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Data corrections: Waste Pro USA HQ is Longwood, FL (source listed 'United States'); Binance YES applies only to Binance.US (Miami) — global Binance.com is a separate entity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>For large Fortune 500 companies (JPM, Sysco, GEICO, Spectrum, Toll Brothers), YES required dedicated FL workforce/asset evidence beyond just nationwide operations.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H207"/>
+  <dimension ref="B2:H207"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col width="8.625" customWidth="1" min="1" max="1"/>
@@ -1410,7 +1277,6 @@
     <col width="95" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="16.5" customHeight="1" thickBot="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -7750,4 +7616,137 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Florida-Connected B2B Prospects</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HQ in FL, dedicated FL business unit/subsidiary, multiple FL offices/branches as a top market, or FL explicitly cited as a strategic market</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>EDGE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Some FL operational presence (1-2 offices, regional rep coverage, distribution touch-point) but FL is one of many markets — not dominant</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>YES — 111 (28 HQ'd in FL + 83 with major FL operations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EDGE — 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NO — remaining rows (no meaningful FL connection)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Methodology notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Pass 1: auto-tagged all 29 companies with HQ listed in Florida (incl. Waste Pro USA — manual correction).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Pass 2: dispatched 6 parallel research agents to assess the remaining ~177 non-FL-HQ companies for major FL operations (multiple FL offices/branches, FL-based subsidiary, FL acquisition history, FL named as top market).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>YES = strong evidence FL is a top-tier operational market. EDGE = some FL presence (1-2 offices, regional coverage) but not dominant. NO = no meaningful FL connection beyond standard nationwide footprint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Data corrections: Waste Pro USA HQ is Longwood, FL (source listed 'United States'); Binance YES applies only to Binance.US (Miami) — global Binance.com is a separate entity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>For large Fortune 500 companies (JPM, Sysco, GEICO, Spectrum, Toll Brothers), YES required dedicated FL workforce/asset evidence beyond just nationwide operations.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>